--- a/research/traditional_assets/database/data/switzerland/switzerland_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,13 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0158</v>
+        <v>0.0249</v>
       </c>
       <c r="E2">
-        <v>0.039</v>
+        <v>0.0223</v>
       </c>
       <c r="F2">
-        <v>0.057</v>
+        <v>0.067</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +603,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>6.340613474386924e-05</v>
+        <v>1.549168978106797e-05</v>
       </c>
       <c r="J2">
-        <v>5.509015272311232e-05</v>
+        <v>1.33416295022158e-05</v>
       </c>
       <c r="K2">
-        <v>1347.89</v>
+        <v>1967.8</v>
       </c>
       <c r="L2">
-        <v>0.3410135100946213</v>
+        <v>0.3532791152762069</v>
       </c>
       <c r="M2">
-        <v>775.3188</v>
+        <v>901.3790000000001</v>
       </c>
       <c r="N2">
-        <v>0.03588741078123698</v>
+        <v>0.02629383623581576</v>
       </c>
       <c r="O2">
-        <v>0.5752092529805845</v>
+        <v>0.4580643358064845</v>
       </c>
       <c r="P2">
-        <v>775.3188</v>
+        <v>900.6540000000001</v>
       </c>
       <c r="Q2">
-        <v>0.03588741078123698</v>
+        <v>0.0262726874945305</v>
       </c>
       <c r="R2">
-        <v>0.5752092529805845</v>
+        <v>0.4576959040552903</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.7249999999999996</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.0008043231537455382</v>
       </c>
       <c r="U2">
-        <v>47388.4</v>
+        <v>66528.89999999999</v>
       </c>
       <c r="V2">
-        <v>2.193480897232945</v>
+        <v>1.940693095300604</v>
       </c>
       <c r="W2">
-        <v>0.05795625942684766</v>
+        <v>0.06072351421188631</v>
       </c>
       <c r="X2">
-        <v>0.1459061618154215</v>
+        <v>0.1402326970431804</v>
       </c>
       <c r="Y2">
-        <v>-0.08794990238857384</v>
+        <v>-0.07950918283129406</v>
       </c>
       <c r="Z2">
-        <v>0.06248229228607002</v>
+        <v>0.05484253523597456</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.04242471515988017</v>
+        <v>0.05702333187053502</v>
       </c>
       <c r="AC2">
-        <v>-0.04242471515988017</v>
+        <v>-0.05702333187053502</v>
       </c>
       <c r="AD2">
-        <v>88455.10000000001</v>
+        <v>134637.6</v>
       </c>
       <c r="AE2">
-        <v>8.516904559056913</v>
+        <v>0.7335486937523664</v>
       </c>
       <c r="AF2">
-        <v>88463.61690455905</v>
+        <v>134638.3335486937</v>
       </c>
       <c r="AG2">
-        <v>41075.21690455905</v>
+        <v>68109.43354869375</v>
       </c>
       <c r="AH2">
-        <v>0.8037191923345475</v>
+        <v>0.7970569781456192</v>
       </c>
       <c r="AI2">
-        <v>0.8117498266387912</v>
+        <v>0.8237539885809978</v>
       </c>
       <c r="AJ2">
-        <v>0.6553222562217454</v>
+        <v>0.6651933309404632</v>
       </c>
       <c r="AK2">
-        <v>0.6669081373064201</v>
+        <v>0.7027681729390073</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>45268.73080859775</v>
+        <v>577843.7768240344</v>
       </c>
       <c r="AP2">
-        <v>21021.0936051991</v>
+        <v>292315.1654450376</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +710,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Banque Cantonale Vaudoise (SWX:BCVN)</t>
+          <t>Basellandschaftliche Kantonalbank (SWX:BLKB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.00651</v>
+        <v>0.0258</v>
       </c>
       <c r="E3">
-        <v>0.02</v>
+        <v>0.0106</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,28 +737,28 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>374.6</v>
+        <v>147</v>
       </c>
       <c r="L3">
-        <v>0.3601923076923077</v>
+        <v>0.3595890410958904</v>
       </c>
       <c r="M3">
-        <v>334.151</v>
+        <v>79.27200000000001</v>
       </c>
       <c r="N3">
-        <v>0.05024902630114739</v>
+        <v>0.0372064207265559</v>
       </c>
       <c r="O3">
-        <v>0.8920208222103577</v>
+        <v>0.5392653061224491</v>
       </c>
       <c r="P3">
-        <v>334.151</v>
+        <v>79.27200000000001</v>
       </c>
       <c r="Q3">
-        <v>0.05024902630114739</v>
+        <v>0.0372064207265559</v>
       </c>
       <c r="R3">
-        <v>0.8920208222103577</v>
+        <v>0.5392653061224491</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,55 +767,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>12650.6</v>
+        <v>6576.6</v>
       </c>
       <c r="V3">
-        <v>1.902374471796568</v>
+        <v>3.086736130667418</v>
       </c>
       <c r="W3">
-        <v>0.1032809484422388</v>
+        <v>0.05296152183311716</v>
       </c>
       <c r="X3">
-        <v>0.09590029612946854</v>
+        <v>0.1543875852304841</v>
       </c>
       <c r="Y3">
-        <v>0.007380652312770228</v>
+        <v>-0.1014260633973669</v>
       </c>
       <c r="Z3">
-        <v>0.1478221812868489</v>
+        <v>0.05929020000290068</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.04233427293663976</v>
+        <v>0.0563823072399615</v>
       </c>
       <c r="AC3">
-        <v>-0.04233427293663976</v>
+        <v>-0.0563823072399615</v>
       </c>
       <c r="AD3">
-        <v>15850</v>
+        <v>11440.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>15850</v>
+        <v>11440.2</v>
       </c>
       <c r="AG3">
-        <v>3199.4</v>
+        <v>4863.6</v>
       </c>
       <c r="AH3">
-        <v>0.704447575322557</v>
+        <v>0.8430011495269254</v>
       </c>
       <c r="AI3">
-        <v>0.8098800253438797</v>
+        <v>0.8049563051462828</v>
       </c>
       <c r="AJ3">
-        <v>0.3248352674809377</v>
+        <v>0.6953761688255984</v>
       </c>
       <c r="AK3">
-        <v>0.4623276783907979</v>
+        <v>0.636963696369637</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zuger Kantonalbank (SWX:ZUGER)</t>
+          <t>Glarner Kantonalbank (SWX:GLKBN)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0325</v>
+        <v>0.0623</v>
       </c>
       <c r="E4">
-        <v>0.039</v>
+        <v>0.0364</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,85 +859,82 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>81</v>
+        <v>23.5</v>
       </c>
       <c r="L4">
-        <v>0.3307472437729685</v>
+        <v>0.2460732984293194</v>
       </c>
       <c r="M4">
-        <v>68.544</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.032313784650198</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.8462222222222222</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>68.544</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.032313784650198</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.8462222222222222</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
-      <c r="T4">
-        <v>0</v>
-      </c>
       <c r="U4">
-        <v>0</v>
+        <v>1464.7</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>4.041666666666667</v>
       </c>
       <c r="W4">
-        <v>0.05705430724801014</v>
+        <v>0.06072351421188631</v>
       </c>
       <c r="X4">
-        <v>0.1071580015185169</v>
+        <v>0.2216244694112129</v>
       </c>
       <c r="Y4">
-        <v>-0.05010369427050675</v>
+        <v>-0.1609009551993266</v>
       </c>
       <c r="Z4">
-        <v>0.03657298169110839</v>
+        <v>0.04845256215119229</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.04236359187663293</v>
+        <v>0.05670736459433195</v>
       </c>
       <c r="AC4">
-        <v>-0.04236359187663293</v>
+        <v>-0.05670736459433195</v>
       </c>
       <c r="AD4">
-        <v>6107.7</v>
+        <v>3334.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>6107.7</v>
+        <v>3334.9</v>
       </c>
       <c r="AG4">
-        <v>6107.7</v>
+        <v>1870.2</v>
       </c>
       <c r="AH4">
-        <v>0.7422255708539416</v>
+        <v>0.9019825277905499</v>
       </c>
       <c r="AI4">
-        <v>0.807010821452638</v>
+        <v>0.8895913358941527</v>
       </c>
       <c r="AJ4">
-        <v>0.7422255708539416</v>
+        <v>0.8376780435366837</v>
       </c>
       <c r="AK4">
-        <v>0.807010821452638</v>
+        <v>0.8187907709820061</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -954,7 +951,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Walliser Kantonalbank (SWX:WKBN)</t>
+          <t>Banque Cantonale du Jura SA (SWX:BCJ)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -963,10 +960,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.00363</v>
+        <v>0.0244</v>
       </c>
       <c r="E5">
-        <v>0.0358</v>
+        <v>0.0187</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -975,100 +972,97 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>4.163060737747262e-05</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>3.928755139815076e-05</v>
+        <v>0</v>
       </c>
       <c r="K5">
-        <v>73.59999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="L5">
-        <v>0.2940471434278865</v>
+        <v>0.1966604823747681</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>4.675</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>0.02648725212464589</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0.4410377358490566</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>3.95</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>0.02237960339943343</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0.3726415094339623</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.7249999999999996</v>
+      </c>
+      <c r="T5">
+        <v>0.1550802139037432</v>
       </c>
       <c r="U5">
-        <v>3494.5</v>
+        <v>985.4</v>
       </c>
       <c r="V5">
-        <v>2.011801957397812</v>
+        <v>5.583002832861189</v>
       </c>
       <c r="W5">
-        <v>0.04916499665998664</v>
+        <v>0.03599320882852292</v>
       </c>
       <c r="X5">
-        <v>0.1237316407001542</v>
+        <v>0.2199050647711085</v>
       </c>
       <c r="Y5">
-        <v>-0.07456664404016755</v>
+        <v>-0.1839118559425856</v>
       </c>
       <c r="Z5">
-        <v>0.05766898551606779</v>
+        <v>0.05452154562006877</v>
       </c>
       <c r="AA5">
-        <v>2.265673232541725e-06</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.04239527584021999</v>
+        <v>0.05671103921279615</v>
       </c>
       <c r="AC5">
-        <v>-0.04239301016698745</v>
+        <v>-0.05671103921279615</v>
       </c>
       <c r="AD5">
-        <v>6269.2</v>
+        <v>1606.9</v>
       </c>
       <c r="AE5">
-        <v>0.287899294867093</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>6269.487899294867</v>
+        <v>1606.9</v>
       </c>
       <c r="AG5">
-        <v>2774.987899294867</v>
+        <v>621.5000000000001</v>
       </c>
       <c r="AH5">
-        <v>0.7830509429542786</v>
+        <v>0.9010317371313222</v>
       </c>
       <c r="AI5">
-        <v>0.8070513445735563</v>
+        <v>0.8434727835809144</v>
       </c>
       <c r="AJ5">
-        <v>0.6150255632840996</v>
+        <v>0.7788220551378446</v>
       </c>
       <c r="AK5">
-        <v>0.6492888827881289</v>
+        <v>0.6757638360334892</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
         <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>92194.11764705881</v>
-      </c>
-      <c r="AP5">
-        <v>40808.64557786569</v>
       </c>
     </row>
     <row r="6">
@@ -1079,7 +1073,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>St. Galler Kantonalbank AG (SWX:SGKN)</t>
+          <t>Zuger Kantonalbank (SWX:ZUGER)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1088,10 +1082,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0199</v>
+        <v>0.0201</v>
       </c>
       <c r="E6">
-        <v>0.0766</v>
+        <v>0.0828</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,103 +1094,94 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.0001489553324078178</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0.0001296438069913917</v>
+        <v>0</v>
       </c>
       <c r="K6">
-        <v>192</v>
+        <v>95.8</v>
       </c>
       <c r="L6">
-        <v>0.3602927378495027</v>
+        <v>0.3788058521154606</v>
       </c>
       <c r="M6">
-        <v>103.454</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.0363455593029792</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.5388229166666667</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>103.454</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.0363455593029792</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.5388229166666667</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>8356.799999999999</v>
+        <v>3784.2</v>
       </c>
       <c r="V6">
-        <v>2.935919055649241</v>
+        <v>1.680149180837366</v>
       </c>
       <c r="W6">
-        <v>0.07152969227330304</v>
+        <v>0.06558948377379159</v>
       </c>
       <c r="X6">
-        <v>0.1338612784976401</v>
+        <v>0.1124759478743843</v>
       </c>
       <c r="Y6">
-        <v>-0.06233158622433706</v>
+        <v>-0.04688646410059273</v>
       </c>
       <c r="Z6">
-        <v>0.07346997526882214</v>
+        <v>0.03341569440957679</v>
       </c>
       <c r="AA6">
-        <v>9.524927293413502e-06</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.04241013543027285</v>
+        <v>0.05680833198334347</v>
       </c>
       <c r="AC6">
-        <v>-0.04240061050297944</v>
+        <v>-0.05680833198334347</v>
       </c>
       <c r="AD6">
-        <v>11543.6</v>
+        <v>6712.6</v>
       </c>
       <c r="AE6">
-        <v>0.1331085167993694</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>11543.7331085168</v>
+        <v>6712.6</v>
       </c>
       <c r="AG6">
-        <v>3186.9331085168</v>
+        <v>2928.400000000001</v>
       </c>
       <c r="AH6">
-        <v>0.8021977991075455</v>
+        <v>0.7487646264877466</v>
       </c>
       <c r="AI6">
-        <v>0.8047086458053622</v>
+        <v>0.8220281904015478</v>
       </c>
       <c r="AJ6">
-        <v>0.5282209768955153</v>
+        <v>0.5652517999498138</v>
       </c>
       <c r="AK6">
-        <v>0.5321814656298518</v>
+        <v>0.6683250793071183</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
         <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>108901.8867924528</v>
-      </c>
-      <c r="AP6">
-        <v>30065.40668412075</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1192,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Basellandschaftliche Kantonalbank (SWX:BLKB)</t>
+          <t>Luzerner Kantonalbank AG (SWX:LUKN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1216,10 +1201,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.00288</v>
+        <v>0.0397</v>
       </c>
       <c r="E7">
-        <v>0.0154</v>
+        <v>0.0222</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1234,85 +1219,82 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>153.7</v>
+        <v>226</v>
       </c>
       <c r="L7">
-        <v>0.4087765957446808</v>
+        <v>0.3826616999661361</v>
       </c>
       <c r="M7">
-        <v>82.24299999999999</v>
+        <v>-0</v>
       </c>
       <c r="N7">
-        <v>0.0381390280096457</v>
+        <v>-0</v>
       </c>
       <c r="O7">
-        <v>0.5350878334417697</v>
+        <v>-0</v>
       </c>
       <c r="P7">
-        <v>82.24299999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q7">
-        <v>0.0381390280096457</v>
+        <v>-0</v>
       </c>
       <c r="R7">
-        <v>0.5350878334417697</v>
+        <v>-0</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
       <c r="U7">
-        <v>5035.9</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>2.335327397514376</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>0.05795625942684766</v>
+        <v>0.0712484237074401</v>
       </c>
       <c r="X7">
-        <v>0.1381757553171113</v>
+        <v>0.1735880952838468</v>
       </c>
       <c r="Y7">
-        <v>-0.0802194958902637</v>
+        <v>-0.1023396715764067</v>
       </c>
       <c r="Z7">
-        <v>0.05412953658782374</v>
+        <v>0.02348123409669211</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.0424156968870798</v>
+        <v>0.05684633992216628</v>
       </c>
       <c r="AC7">
-        <v>-0.0424156968870798</v>
+        <v>-0.05684633992216628</v>
       </c>
       <c r="AD7">
-        <v>9155.200000000001</v>
+        <v>24516.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>9155.200000000001</v>
+        <v>24516.6</v>
       </c>
       <c r="AG7">
-        <v>4119.300000000001</v>
+        <v>24516.6</v>
       </c>
       <c r="AH7">
-        <v>0.8093638388910499</v>
+        <v>0.8660232996813779</v>
       </c>
       <c r="AI7">
-        <v>0.7673584336339558</v>
+        <v>0.8859073498590735</v>
       </c>
       <c r="AJ7">
-        <v>0.6563889287250826</v>
+        <v>0.8660232996813779</v>
       </c>
       <c r="AK7">
-        <v>0.5974415872601488</v>
+        <v>0.8859073498590735</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1329,7 +1311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Thurgauer Kantonalbank (SWX:TKBP)</t>
+          <t>Valiant Holding AG (SWX:VATN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1338,10 +1320,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0234</v>
+        <v>0.0334</v>
       </c>
       <c r="E8">
-        <v>0.06179999999999999</v>
+        <v>0.0116</v>
+      </c>
+      <c r="F8">
+        <v>0.067</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1356,28 +1341,28 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>154.4</v>
+        <v>129.4</v>
       </c>
       <c r="L8">
-        <v>0.3977331272539928</v>
+        <v>0.2863465368444346</v>
       </c>
       <c r="M8">
-        <v>64.80000000000001</v>
+        <v>80.422</v>
       </c>
       <c r="N8">
-        <v>0.02781115879828327</v>
+        <v>0.04708823701621875</v>
       </c>
       <c r="O8">
-        <v>0.4196891191709845</v>
+        <v>0.6214992272024729</v>
       </c>
       <c r="P8">
-        <v>64.80000000000001</v>
+        <v>80.422</v>
       </c>
       <c r="Q8">
-        <v>0.02781115879828327</v>
+        <v>0.04708823701621875</v>
       </c>
       <c r="R8">
-        <v>0.4196891191709845</v>
+        <v>0.6214992272024729</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1386,55 +1371,55 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>6367.9</v>
+        <v>5460</v>
       </c>
       <c r="V8">
-        <v>2.733004291845493</v>
+        <v>3.196908484103285</v>
       </c>
       <c r="W8">
-        <v>0.06524954570426404</v>
+        <v>0.05103731166679814</v>
       </c>
       <c r="X8">
-        <v>0.1459061618154215</v>
+        <v>0.1721661317230974</v>
       </c>
       <c r="Y8">
-        <v>-0.08065661611115744</v>
+        <v>-0.1211288200562992</v>
       </c>
       <c r="Z8">
-        <v>0.0565839722473253</v>
+        <v>0.06553549416285984</v>
       </c>
       <c r="AA8">
         <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.04242471515988017</v>
+        <v>0.05685202483642058</v>
       </c>
       <c r="AC8">
-        <v>-0.04242471515988017</v>
+        <v>-0.05685202483642058</v>
       </c>
       <c r="AD8">
-        <v>10685.6</v>
+        <v>10901.4</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>10685.6</v>
+        <v>10901.4</v>
       </c>
       <c r="AG8">
-        <v>4317.700000000001</v>
+        <v>5441.4</v>
       </c>
       <c r="AH8">
-        <v>0.8209840499093396</v>
+        <v>0.8645523542147463</v>
       </c>
       <c r="AI8">
-        <v>0.806454290911012</v>
+        <v>0.8162724352494554</v>
       </c>
       <c r="AJ8">
-        <v>0.6495028355671887</v>
+        <v>0.7611094792497168</v>
       </c>
       <c r="AK8">
-        <v>0.627372061259481</v>
+        <v>0.6892122962343732</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1451,7 +1436,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Valiant Holding AG (SWX:VATN)</t>
+          <t>Berner Kantonalbank AG (SWX:BEKN)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1460,13 +1445,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.014</v>
+        <v>0.0134</v>
       </c>
       <c r="E9">
-        <v>0.0068</v>
-      </c>
-      <c r="F9">
-        <v>0.057</v>
+        <v>0.0375</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1481,28 +1463,28 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>131.6</v>
+        <v>164.7</v>
       </c>
       <c r="L9">
-        <v>0.2882172579938677</v>
+        <v>0.3313216656608328</v>
       </c>
       <c r="M9">
-        <v>84.688</v>
+        <v>88.98120000000002</v>
       </c>
       <c r="N9">
-        <v>0.05369515597260969</v>
+        <v>0.04003473409520383</v>
       </c>
       <c r="O9">
-        <v>0.6435258358662614</v>
+        <v>0.5402622950819673</v>
       </c>
       <c r="P9">
-        <v>84.688</v>
+        <v>88.98120000000002</v>
       </c>
       <c r="Q9">
-        <v>0.05369515597260969</v>
+        <v>0.04003473409520383</v>
       </c>
       <c r="R9">
-        <v>0.6435258358662614</v>
+        <v>0.5402622950819673</v>
       </c>
       <c r="S9">
         <v>0</v>
@@ -1511,55 +1493,55 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>7396.2</v>
+        <v>8531.299999999999</v>
       </c>
       <c r="V9">
-        <v>4.6894496576211</v>
+        <v>3.838432466480698</v>
       </c>
       <c r="W9">
-        <v>0.05188046992036584</v>
+        <v>0.05784630514189379</v>
       </c>
       <c r="X9">
-        <v>0.2110143920249383</v>
+        <v>0.1402326970431804</v>
       </c>
       <c r="Y9">
-        <v>-0.1591339221045724</v>
+        <v>-0.08238639190128658</v>
       </c>
       <c r="Z9">
-        <v>0.06173273484397816</v>
+        <v>0.1690183944782564</v>
       </c>
       <c r="AA9">
         <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.04247184481334295</v>
+        <v>0.05702333187053502</v>
       </c>
       <c r="AC9">
-        <v>-0.04247184481334295</v>
+        <v>-0.05702333187053502</v>
       </c>
       <c r="AD9">
-        <v>11756.3</v>
+        <v>10140.8</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>11756.3</v>
+        <v>10140.8</v>
       </c>
       <c r="AG9">
-        <v>4360.099999999999</v>
+        <v>1609.5</v>
       </c>
       <c r="AH9">
-        <v>0.8817114786065173</v>
+        <v>0.8202274455246938</v>
       </c>
       <c r="AI9">
-        <v>0.8225963321368347</v>
+        <v>0.7823423673633131</v>
       </c>
       <c r="AJ9">
-        <v>0.7343573678271268</v>
+        <v>0.4200046971634352</v>
       </c>
       <c r="AK9">
-        <v>0.6323109274164309</v>
+        <v>0.3632526857452379</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1576,7 +1558,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Banque Cantonale du Jura SA (SWX:BCJ)</t>
+          <t>Thurgauer Kantonalbank (SWX:TKBP)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1585,10 +1567,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0142</v>
+        <v>0.0197</v>
       </c>
       <c r="E10">
-        <v>-0.0209</v>
+        <v>0.0223</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1603,82 +1585,85 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>8.59</v>
+        <v>153.5</v>
       </c>
       <c r="L10">
-        <v>0.1763860369609856</v>
+        <v>0.3963335915311128</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>65</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.02525350635222813</v>
       </c>
       <c r="O10">
-        <v>-0</v>
+        <v>0.4234527687296417</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>65</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.02525350635222813</v>
       </c>
       <c r="R10">
-        <v>-0</v>
+        <v>0.4234527687296417</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>921.7</v>
+        <v>5682.4</v>
       </c>
       <c r="V10">
-        <v>5.358720930232558</v>
+        <v>2.207700376860018</v>
       </c>
       <c r="W10">
-        <v>0.03167404129793511</v>
+        <v>0.05985572236303373</v>
       </c>
       <c r="X10">
-        <v>0.2656639725444806</v>
+        <v>0.1322180461917942</v>
       </c>
       <c r="Y10">
-        <v>-0.2339899312465455</v>
+        <v>-0.0723623238287605</v>
       </c>
       <c r="Z10">
-        <v>0.04159904330742292</v>
+        <v>0.05627560954345993</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.04249219094205142</v>
+        <v>0.05708550262472295</v>
       </c>
       <c r="AC10">
-        <v>-0.04249219094205142</v>
+        <v>-0.05708550262472295</v>
       </c>
       <c r="AD10">
-        <v>1696.1</v>
+        <v>10567.7</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>1696.1</v>
+        <v>10567.7</v>
       </c>
       <c r="AG10">
-        <v>774.3999999999999</v>
+        <v>4885.300000000001</v>
       </c>
       <c r="AH10">
-        <v>0.9079278411219956</v>
+        <v>0.8041410482741828</v>
       </c>
       <c r="AI10">
-        <v>0.8555359394703657</v>
+        <v>0.8031021537245604</v>
       </c>
       <c r="AJ10">
-        <v>0.8182586644125105</v>
+        <v>0.6549361861861863</v>
       </c>
       <c r="AK10">
-        <v>0.7300150829562595</v>
+        <v>0.6534469382841551</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1695,7 +1680,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Banque Cantonale de Genève SA (SWX:BCGE)</t>
+          <t>St. Galler Kantonalbank AG (SWX:SGKN)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1704,10 +1689,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0296</v>
+        <v>0.0249</v>
       </c>
       <c r="E11">
-        <v>0.08539999999999999</v>
+        <v>0.0318</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1716,34 +1701,34 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>0.0002196390522287437</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>0.0001854818036000422</v>
       </c>
       <c r="K11">
-        <v>123.3</v>
+        <v>186.9</v>
       </c>
       <c r="L11">
-        <v>0.2939914163090129</v>
+        <v>0.3483041371598956</v>
       </c>
       <c r="M11">
-        <v>28.7448</v>
+        <v>106.444</v>
       </c>
       <c r="N11">
-        <v>0.02312534191472244</v>
+        <v>0.03422086481273108</v>
       </c>
       <c r="O11">
-        <v>0.2331289537712895</v>
+        <v>0.5695238095238095</v>
       </c>
       <c r="P11">
-        <v>28.7448</v>
+        <v>106.444</v>
       </c>
       <c r="Q11">
-        <v>0.02312534191472244</v>
+        <v>0.03422086481273108</v>
       </c>
       <c r="R11">
-        <v>0.2331289537712895</v>
+        <v>0.5695238095238095</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1752,61 +1737,67 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>8243.700000000001</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>2.65028130525639</v>
       </c>
       <c r="W11">
-        <v>0.0697477090168571</v>
+        <v>0.0667142602177405</v>
       </c>
       <c r="X11">
-        <v>0.2060828178226533</v>
+        <v>0.1282824023083361</v>
       </c>
       <c r="Y11">
-        <v>-0.1363351088057961</v>
+        <v>-0.06156814209059557</v>
       </c>
       <c r="Z11">
-        <v>0.0362948575535016</v>
+        <v>0.08963904435640642</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.662641162021044e-05</v>
       </c>
       <c r="AB11">
-        <v>0.0430328928500672</v>
+        <v>0.05712029247107531</v>
       </c>
       <c r="AC11">
-        <v>-0.0430328928500672</v>
+        <v>-0.0571036660594551</v>
       </c>
       <c r="AD11">
-        <v>8995.200000000001</v>
+        <v>12072.7</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>0.2907084228702805</v>
       </c>
       <c r="AF11">
-        <v>8995.200000000001</v>
+        <v>12072.99070842287</v>
       </c>
       <c r="AG11">
-        <v>8995.200000000001</v>
+        <v>3829.29070842287</v>
       </c>
       <c r="AH11">
-        <v>0.8785919399894513</v>
+        <v>0.7951393352337296</v>
       </c>
       <c r="AI11">
-        <v>0.8257931844888367</v>
+        <v>0.8117283604509817</v>
       </c>
       <c r="AJ11">
-        <v>0.8785919399894513</v>
+        <v>0.5517876358685045</v>
       </c>
       <c r="AK11">
-        <v>0.8257931844888367</v>
+        <v>0.5776146127722447</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
         <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>68594.88636363637</v>
+      </c>
+      <c r="AP11">
+        <v>21757.33357058449</v>
       </c>
     </row>
     <row r="12">
@@ -1817,7 +1808,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Glarner Kantonalbank (SWX:GLKBN)</t>
+          <t>Walliser Kantonalbank (SWX:WKBN)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1826,10 +1817,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.062</v>
+        <v>0.0104</v>
       </c>
       <c r="E12">
-        <v>0.06900000000000001</v>
+        <v>-0.0185</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1838,16 +1829,16 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>-0.0001210895825716041</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>-9.976906916170537e-05</v>
       </c>
       <c r="K12">
-        <v>26.6</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="L12">
-        <v>0.2835820895522388</v>
+        <v>0.2796317606444189</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1871,61 +1862,67 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>1338.1</v>
+        <v>3467.3</v>
       </c>
       <c r="V12">
-        <v>3.881926312735712</v>
+        <v>1.962474530224134</v>
       </c>
       <c r="W12">
-        <v>0.06983460225781046</v>
+        <v>0.04863566615518047</v>
       </c>
       <c r="X12">
-        <v>0.2342469580704486</v>
+        <v>0.1279680939373795</v>
       </c>
       <c r="Y12">
-        <v>-0.1644123558126381</v>
+        <v>-0.07933242778219904</v>
       </c>
       <c r="Z12">
-        <v>0.0468017163955693</v>
+        <v>0.06099611298783267</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>-6.085525415278273e-06</v>
       </c>
       <c r="AB12">
-        <v>0.0430554183830916</v>
+        <v>0.0571232092587371</v>
       </c>
       <c r="AC12">
-        <v>-0.0430554183830916</v>
+        <v>-0.05712929478415237</v>
       </c>
       <c r="AD12">
-        <v>2922.1</v>
+        <v>6825.5</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>0.4428402708820859</v>
       </c>
       <c r="AF12">
-        <v>2922.1</v>
+        <v>6825.942840270882</v>
       </c>
       <c r="AG12">
-        <v>1584</v>
+        <v>3358.642840270882</v>
       </c>
       <c r="AH12">
-        <v>0.894483898616383</v>
+        <v>0.7943846298157921</v>
       </c>
       <c r="AI12">
-        <v>0.8830497718412862</v>
+        <v>0.8196728619606418</v>
       </c>
       <c r="AJ12">
-        <v>0.8212785814279048</v>
+        <v>0.6552883223829643</v>
       </c>
       <c r="AK12">
-        <v>0.8036529680365296</v>
+        <v>0.691030026203603</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>119745.6140350877</v>
+      </c>
+      <c r="AP12">
+        <v>58923.55860124354</v>
       </c>
     </row>
     <row r="13">
@@ -1936,7 +1933,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bank Linth LLB AG (SWX:LINN)</t>
+          <t>Graubündner Kantonalbank (SWX:GRKP)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1945,10 +1942,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0158</v>
+        <v>0.0373</v>
       </c>
       <c r="E13">
-        <v>0.0675</v>
+        <v>0.00873</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1957,34 +1954,34 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.001579770633810512</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>0.001337882904716676</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>28.5</v>
+        <v>190.5</v>
       </c>
       <c r="L13">
-        <v>0.2799607072691552</v>
+        <v>0.4110919292188174</v>
       </c>
       <c r="M13">
-        <v>8.694000000000001</v>
+        <v>110.805</v>
       </c>
       <c r="N13">
-        <v>0.02038930581613509</v>
+        <v>0.02425360066541172</v>
       </c>
       <c r="O13">
-        <v>0.3050526315789474</v>
+        <v>0.5816535433070866</v>
       </c>
       <c r="P13">
-        <v>8.694000000000001</v>
+        <v>110.805</v>
       </c>
       <c r="Q13">
-        <v>0.02038930581613509</v>
+        <v>0.02425360066541172</v>
       </c>
       <c r="R13">
-        <v>0.3050526315789474</v>
+        <v>0.5816535433070866</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1993,55 +1990,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>1826.7</v>
+        <v>8799.700000000001</v>
       </c>
       <c r="V13">
-        <v>4.284005628517824</v>
+        <v>1.926126165564943</v>
       </c>
       <c r="W13">
-        <v>0.05156504432784512</v>
+        <v>0.06544142906217795</v>
       </c>
       <c r="X13">
-        <v>0.2271925146875506</v>
+        <v>0.1016790178200009</v>
       </c>
       <c r="Y13">
-        <v>-0.1756274703597055</v>
+        <v>-0.03623758875782299</v>
       </c>
       <c r="Z13">
-        <v>0.05088229558800027</v>
+        <v>0.03263242398208526</v>
       </c>
       <c r="AA13">
-        <v>6.807455341992634e-05</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.0482878995789441</v>
+        <v>0.05747712395431227</v>
       </c>
       <c r="AC13">
-        <v>-0.04821982502552417</v>
+        <v>-0.05747712395431227</v>
       </c>
       <c r="AD13">
-        <v>3474.1</v>
+        <v>10804.1</v>
       </c>
       <c r="AE13">
-        <v>8.09589674739045</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>3482.19589674739</v>
+        <v>10804.1</v>
       </c>
       <c r="AG13">
-        <v>1655.49589674739</v>
+        <v>2004.4</v>
       </c>
       <c r="AH13">
-        <v>0.8909071156844747</v>
+        <v>0.7028108269855002</v>
       </c>
       <c r="AI13">
-        <v>0.8557454556392323</v>
+        <v>0.7887355818367645</v>
       </c>
       <c r="AJ13">
-        <v>0.7951866850469431</v>
+        <v>0.3049444698006998</v>
       </c>
       <c r="AK13">
-        <v>0.7382380940578712</v>
+        <v>0.4092031929444909</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2049,11 +2046,249 @@
       <c r="AM13">
         <v>0</v>
       </c>
-      <c r="AN13">
-        <v>1951.741573033708</v>
-      </c>
-      <c r="AP13">
-        <v>930.0538745771854</v>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Banque Cantonale Vaudoise (SWX:BCVN)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>0.0134</v>
+      </c>
+      <c r="E14">
+        <v>0.049</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>421.2</v>
+      </c>
+      <c r="L14">
+        <v>0.3880239520958084</v>
+      </c>
+      <c r="M14">
+        <v>332.433</v>
+      </c>
+      <c r="N14">
+        <v>0.04033499963600185</v>
+      </c>
+      <c r="O14">
+        <v>0.7892521367521369</v>
+      </c>
+      <c r="P14">
+        <v>332.433</v>
+      </c>
+      <c r="Q14">
+        <v>0.04033499963600185</v>
+      </c>
+      <c r="R14">
+        <v>0.7892521367521369</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>13533.6</v>
+      </c>
+      <c r="V14">
+        <v>1.642068480186367</v>
+      </c>
+      <c r="W14">
+        <v>0.1132014620511718</v>
+      </c>
+      <c r="X14">
+        <v>0.09769512371786335</v>
+      </c>
+      <c r="Y14">
+        <v>0.01550633833330843</v>
+      </c>
+      <c r="Z14">
+        <v>0.1568841124304825</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.05756025353654513</v>
+      </c>
+      <c r="AC14">
+        <v>-0.05756025353654513</v>
+      </c>
+      <c r="AD14">
+        <v>17619</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>17619</v>
+      </c>
+      <c r="AG14">
+        <v>4085.4</v>
+      </c>
+      <c r="AH14">
+        <v>0.6813014291901256</v>
+      </c>
+      <c r="AI14">
+        <v>0.8267328591002084</v>
+      </c>
+      <c r="AJ14">
+        <v>0.3314134596664287</v>
+      </c>
+      <c r="AK14">
+        <v>0.5252507071226535</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Banque Cantonale de Genève SA (SWX:BCGE)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.0505</v>
+      </c>
+      <c r="E15">
+        <v>0.108</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>145.8</v>
+      </c>
+      <c r="L15">
+        <v>0.3000617410989916</v>
+      </c>
+      <c r="M15">
+        <v>33.3468</v>
+      </c>
+      <c r="N15">
+        <v>0.02426457105435495</v>
+      </c>
+      <c r="O15">
+        <v>0.228716049382716</v>
+      </c>
+      <c r="P15">
+        <v>33.3468</v>
+      </c>
+      <c r="Q15">
+        <v>0.02426457105435495</v>
+      </c>
+      <c r="R15">
+        <v>0.228716049382716</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.07685009487666035</v>
+      </c>
+      <c r="X15">
+        <v>0.1635262616520862</v>
+      </c>
+      <c r="Y15">
+        <v>-0.08667616677542582</v>
+      </c>
+      <c r="Z15">
+        <v>0.04461181705427409</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0.05822133060757824</v>
+      </c>
+      <c r="AC15">
+        <v>-0.05822133060757824</v>
+      </c>
+      <c r="AD15">
+        <v>8095.2</v>
+      </c>
+      <c r="AE15">
+        <v>0</v>
+      </c>
+      <c r="AF15">
+        <v>8095.2</v>
+      </c>
+      <c r="AG15">
+        <v>8095.2</v>
+      </c>
+      <c r="AH15">
+        <v>0.8548709013147473</v>
+      </c>
+      <c r="AI15">
+        <v>0.8052842050812724</v>
+      </c>
+      <c r="AJ15">
+        <v>0.8548709013147473</v>
+      </c>
+      <c r="AK15">
+        <v>0.8052842050812724</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_banks_regional.xlsx
@@ -588,13 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0249</v>
+        <v>0.0491</v>
       </c>
       <c r="E2">
-        <v>0.0223</v>
-      </c>
-      <c r="F2">
-        <v>0.067</v>
+        <v>0.0408</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -603,91 +600,91 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1.549168978106797e-05</v>
+        <v>1.955678200419801e-05</v>
       </c>
       <c r="J2">
-        <v>1.33416295022158e-05</v>
+        <v>1.672861819999401e-05</v>
       </c>
       <c r="K2">
-        <v>1967.8</v>
+        <v>2129.9</v>
       </c>
       <c r="L2">
-        <v>0.3532791152762069</v>
+        <v>0.3575157364666387</v>
       </c>
       <c r="M2">
-        <v>901.3790000000001</v>
+        <v>778.7814000000001</v>
       </c>
       <c r="N2">
-        <v>0.02629383623581576</v>
+        <v>0.02137178407067018</v>
       </c>
       <c r="O2">
-        <v>0.4580643358064845</v>
+        <v>0.3656422367247289</v>
       </c>
       <c r="P2">
-        <v>900.6540000000001</v>
+        <v>778.7814000000001</v>
       </c>
       <c r="Q2">
-        <v>0.0262726874945305</v>
+        <v>0.02137178407067018</v>
       </c>
       <c r="R2">
-        <v>0.4576959040552903</v>
+        <v>0.3656422367247289</v>
       </c>
       <c r="S2">
-        <v>0.7249999999999996</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.0008043231537455382</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>66528.89999999999</v>
+        <v>66499.89999999999</v>
       </c>
       <c r="V2">
-        <v>1.940693095300604</v>
+        <v>1.824929952771291</v>
       </c>
       <c r="W2">
-        <v>0.06072351421188631</v>
+        <v>0.0670258391521639</v>
       </c>
       <c r="X2">
-        <v>0.1402326970431804</v>
+        <v>0.09799984411196272</v>
       </c>
       <c r="Y2">
-        <v>-0.07950918283129406</v>
+        <v>-0.03097400495979882</v>
       </c>
       <c r="Z2">
-        <v>0.05484253523597456</v>
+        <v>0.08121673650798619</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05702333187053502</v>
+        <v>0.05048678373674157</v>
       </c>
       <c r="AC2">
-        <v>-0.05702333187053502</v>
+        <v>-0.05049396047167493</v>
       </c>
       <c r="AD2">
-        <v>134637.6</v>
+        <v>112369.1</v>
       </c>
       <c r="AE2">
-        <v>0.7335486937523664</v>
+        <v>0.7024523560499518</v>
       </c>
       <c r="AF2">
-        <v>134638.3335486937</v>
+        <v>112369.802452356</v>
       </c>
       <c r="AG2">
-        <v>68109.43354869375</v>
+        <v>45869.90245235605</v>
       </c>
       <c r="AH2">
-        <v>0.7970569781456192</v>
+        <v>0.7551251808555249</v>
       </c>
       <c r="AI2">
-        <v>0.8237539885809978</v>
+        <v>0.793901708516152</v>
       </c>
       <c r="AJ2">
-        <v>0.6651933309404632</v>
+        <v>0.5572849471470513</v>
       </c>
       <c r="AK2">
-        <v>0.7027681729390073</v>
+        <v>0.6112620777268489</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -696,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="AN2">
-        <v>577843.7768240344</v>
+        <v>437233.8521400779</v>
       </c>
       <c r="AP2">
-        <v>292315.1654450376</v>
+        <v>178482.1107095566</v>
       </c>
     </row>
     <row r="3">
@@ -710,7 +707,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Basellandschaftliche Kantonalbank (SWX:BLKB)</t>
+          <t>Glarner Kantonalbank (SWX:GLKBN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -719,10 +716,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0258</v>
+        <v>0.0649</v>
       </c>
       <c r="E3">
-        <v>0.0106</v>
+        <v>0.0486</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -737,85 +734,82 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>147</v>
+        <v>29.8</v>
       </c>
       <c r="L3">
-        <v>0.3595890410958904</v>
+        <v>0.2687105500450856</v>
       </c>
       <c r="M3">
-        <v>79.27200000000001</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.0372064207265559</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.5392653061224491</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>79.27200000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.0372064207265559</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.5392653061224491</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>6576.6</v>
+        <v>1767.8</v>
       </c>
       <c r="V3">
-        <v>3.086736130667418</v>
+        <v>4.815581585399073</v>
       </c>
       <c r="W3">
-        <v>0.05296152183311716</v>
+        <v>0.07088487155090391</v>
       </c>
       <c r="X3">
-        <v>0.1543875852304841</v>
+        <v>0.1795209841974771</v>
       </c>
       <c r="Y3">
-        <v>-0.1014260633973669</v>
+        <v>-0.1086361126465731</v>
       </c>
       <c r="Z3">
-        <v>0.05929020000290068</v>
+        <v>0.04960193219429287</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.0563823072399615</v>
+        <v>0.05015491207103377</v>
       </c>
       <c r="AC3">
-        <v>-0.0563823072399615</v>
+        <v>-0.05015491207103377</v>
       </c>
       <c r="AD3">
-        <v>11440.2</v>
+        <v>4063.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>11440.2</v>
+        <v>4063.1</v>
       </c>
       <c r="AG3">
-        <v>4863.6</v>
+        <v>2295.3</v>
       </c>
       <c r="AH3">
-        <v>0.8430011495269254</v>
+        <v>0.9171369238409102</v>
       </c>
       <c r="AI3">
-        <v>0.8049563051462828</v>
+        <v>0.8979424959667618</v>
       </c>
       <c r="AJ3">
-        <v>0.6953761688255984</v>
+        <v>0.8621168870192308</v>
       </c>
       <c r="AK3">
-        <v>0.636963696369637</v>
+        <v>0.8325051684741214</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -832,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glarner Kantonalbank (SWX:GLKBN)</t>
+          <t>Banque Cantonale du Jura SA (SWX:BCJ)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -841,10 +835,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0623</v>
+        <v>0.0508</v>
       </c>
       <c r="E4">
-        <v>0.0364</v>
+        <v>0.0337</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -859,10 +853,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>23.5</v>
+        <v>13</v>
       </c>
       <c r="L4">
-        <v>0.2460732984293194</v>
+        <v>0.1943198804185351</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,55 +880,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1464.7</v>
+        <v>916.6</v>
       </c>
       <c r="V4">
-        <v>4.041666666666667</v>
+        <v>4.773958333333334</v>
       </c>
       <c r="W4">
-        <v>0.06072351421188631</v>
+        <v>0.04359490274983233</v>
       </c>
       <c r="X4">
-        <v>0.2216244694112129</v>
+        <v>0.1479816444461206</v>
       </c>
       <c r="Y4">
-        <v>-0.1609009551993266</v>
+        <v>-0.1043867416962882</v>
       </c>
       <c r="Z4">
-        <v>0.04845256215119229</v>
+        <v>0.07274111123192345</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05670736459433195</v>
+        <v>0.05021094960816305</v>
       </c>
       <c r="AC4">
-        <v>-0.05670736459433195</v>
+        <v>-0.05021094960816305</v>
       </c>
       <c r="AD4">
-        <v>3334.9</v>
+        <v>1598.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3334.9</v>
+        <v>1598.4</v>
       </c>
       <c r="AG4">
-        <v>1870.2</v>
+        <v>681.8000000000001</v>
       </c>
       <c r="AH4">
-        <v>0.9019825277905499</v>
+        <v>0.8927613941018767</v>
       </c>
       <c r="AI4">
-        <v>0.8895913358941527</v>
+        <v>0.8303376623376624</v>
       </c>
       <c r="AJ4">
-        <v>0.8376780435366837</v>
+        <v>0.7802700846875715</v>
       </c>
       <c r="AK4">
-        <v>0.8187907709820061</v>
+        <v>0.6761205870686235</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -951,7 +945,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Banque Cantonale du Jura SA (SWX:BCJ)</t>
+          <t>Basellandschaftliche Kantonalbank (SWX:BLKB)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -960,10 +954,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0244</v>
+        <v>0.0321</v>
       </c>
       <c r="E5">
-        <v>0.0187</v>
+        <v>0.0118</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -978,85 +972,82 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>10.6</v>
+        <v>157.8</v>
       </c>
       <c r="L5">
-        <v>0.1966604823747681</v>
+        <v>0.3320707070707071</v>
       </c>
       <c r="M5">
-        <v>4.675</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.02648725212464589</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.4410377358490566</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>3.95</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.02237960339943343</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.3726415094339623</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>0.7249999999999996</v>
-      </c>
-      <c r="T5">
-        <v>0.1550802139037432</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>985.4</v>
+        <v>6737.8</v>
       </c>
       <c r="V5">
-        <v>5.583002832861189</v>
+        <v>3.062497159220036</v>
       </c>
       <c r="W5">
-        <v>0.03599320882852292</v>
+        <v>0.05692640692640693</v>
       </c>
       <c r="X5">
-        <v>0.2199050647711085</v>
+        <v>0.1084066428509598</v>
       </c>
       <c r="Y5">
-        <v>-0.1839118559425856</v>
+        <v>-0.05148023592455291</v>
       </c>
       <c r="Z5">
-        <v>0.05452154562006877</v>
+        <v>0.06223479490806223</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05671103921279615</v>
+        <v>0.05024886465051894</v>
       </c>
       <c r="AC5">
-        <v>-0.05671103921279615</v>
+        <v>-0.05024886465051894</v>
       </c>
       <c r="AD5">
-        <v>1606.9</v>
+        <v>10743.1</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1606.9</v>
+        <v>10743.1</v>
       </c>
       <c r="AG5">
-        <v>621.5000000000001</v>
+        <v>4005.3</v>
       </c>
       <c r="AH5">
-        <v>0.9010317371313222</v>
+        <v>0.8300188515977501</v>
       </c>
       <c r="AI5">
-        <v>0.8434727835809144</v>
+        <v>0.7777753645222478</v>
       </c>
       <c r="AJ5">
-        <v>0.7788220551378446</v>
+        <v>0.6454539594546685</v>
       </c>
       <c r="AK5">
-        <v>0.6757638360334892</v>
+        <v>0.5661361451913836</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1064,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zuger Kantonalbank (SWX:ZUGER)</t>
+          <t>Valiant Holding AG (SWX:VATN)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1082,10 +1073,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0201</v>
+        <v>0.0491</v>
       </c>
       <c r="E6">
-        <v>0.0828</v>
+        <v>0.0254</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,82 +1091,85 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>95.8</v>
+        <v>149.5</v>
       </c>
       <c r="L6">
-        <v>0.3788058521154606</v>
+        <v>0.2603169075396135</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>86.426</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.04830427006483345</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.5781003344481606</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>86.426</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.04830427006483345</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.5781003344481606</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>3784.2</v>
+        <v>6108.5</v>
       </c>
       <c r="V6">
-        <v>1.680149180837366</v>
+        <v>3.414095685222446</v>
       </c>
       <c r="W6">
-        <v>0.06558948377379159</v>
+        <v>0.06092839385417941</v>
       </c>
       <c r="X6">
-        <v>0.1124759478743843</v>
+        <v>0.1296992699514897</v>
       </c>
       <c r="Y6">
-        <v>-0.04688646410059273</v>
+        <v>-0.06877087609731032</v>
       </c>
       <c r="Z6">
-        <v>0.03341569440957679</v>
+        <v>0.07274132056592064</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05680833198334347</v>
+        <v>0.05026163032591283</v>
       </c>
       <c r="AC6">
-        <v>-0.05680833198334347</v>
+        <v>-0.05026163032591283</v>
       </c>
       <c r="AD6">
-        <v>6712.6</v>
+        <v>12050.1</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>6712.6</v>
+        <v>12050.1</v>
       </c>
       <c r="AG6">
-        <v>2928.400000000001</v>
+        <v>5941.6</v>
       </c>
       <c r="AH6">
-        <v>0.7487646264877466</v>
+        <v>0.870716004422189</v>
       </c>
       <c r="AI6">
-        <v>0.8220281904015478</v>
+        <v>0.81371761194433</v>
       </c>
       <c r="AJ6">
-        <v>0.5652517999498138</v>
+        <v>0.768562115175661</v>
       </c>
       <c r="AK6">
-        <v>0.6683250793071183</v>
+        <v>0.6829268292682926</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1192,7 +1186,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Luzerner Kantonalbank AG (SWX:LUKN)</t>
+          <t>Berner Kantonalbank AG (SWX:BEKN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1201,10 +1195,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0397</v>
+        <v>0.06309999999999999</v>
       </c>
       <c r="E7">
-        <v>0.0222</v>
+        <v>0.0408</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1219,82 +1213,85 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>226</v>
+        <v>189.1</v>
       </c>
       <c r="L7">
-        <v>0.3826616999661361</v>
+        <v>0.3219819513025711</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>99.08199999999999</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.03817453284530919</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.5239661554732945</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>99.08199999999999</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.03817453284530919</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.5239661554732945</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>0</v>
+        <v>9540.700000000001</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>3.675862068965518</v>
       </c>
       <c r="W7">
-        <v>0.0712484237074401</v>
+        <v>0.0670258391521639</v>
       </c>
       <c r="X7">
-        <v>0.1735880952838468</v>
+        <v>0.09799984411196272</v>
       </c>
       <c r="Y7">
-        <v>-0.1023396715764067</v>
+        <v>-0.03097400495979882</v>
       </c>
       <c r="Z7">
-        <v>0.02348123409669211</v>
+        <v>0.1325494267400921</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05684633992216628</v>
+        <v>0.05042624386450563</v>
       </c>
       <c r="AC7">
-        <v>-0.05684633992216628</v>
+        <v>-0.05042624386450563</v>
       </c>
       <c r="AD7">
-        <v>24516.6</v>
+        <v>10324.6</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>24516.6</v>
+        <v>10324.6</v>
       </c>
       <c r="AG7">
-        <v>24516.6</v>
+        <v>783.8999999999996</v>
       </c>
       <c r="AH7">
-        <v>0.8660232996813779</v>
+        <v>0.7991114619855884</v>
       </c>
       <c r="AI7">
-        <v>0.8859073498590735</v>
+        <v>0.7691665859600242</v>
       </c>
       <c r="AJ7">
-        <v>0.8660232996813779</v>
+        <v>0.2319642540095874</v>
       </c>
       <c r="AK7">
-        <v>0.8859073498590735</v>
+        <v>0.2019111889552853</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1311,7 +1308,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Valiant Holding AG (SWX:VATN)</t>
+          <t>St. Galler Kantonalbank AG (SWX:SGKN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1320,13 +1317,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0334</v>
+        <v>0.0235</v>
       </c>
       <c r="E8">
-        <v>0.0116</v>
-      </c>
-      <c r="F8">
-        <v>0.067</v>
+        <v>0.0512</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1335,34 +1329,34 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>0.0002639727052718075</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>0.0002223032231122908</v>
       </c>
       <c r="K8">
-        <v>129.4</v>
+        <v>224.6</v>
       </c>
       <c r="L8">
-        <v>0.2863465368444346</v>
+        <v>0.3745830553702468</v>
       </c>
       <c r="M8">
-        <v>80.422</v>
+        <v>113.62</v>
       </c>
       <c r="N8">
-        <v>0.04708823701621875</v>
+        <v>0.03253163832102159</v>
       </c>
       <c r="O8">
-        <v>0.6214992272024729</v>
+        <v>0.5058771148708816</v>
       </c>
       <c r="P8">
-        <v>80.422</v>
+        <v>113.62</v>
       </c>
       <c r="Q8">
-        <v>0.04708823701621875</v>
+        <v>0.03253163832102159</v>
       </c>
       <c r="R8">
-        <v>0.6214992272024729</v>
+        <v>0.5058771148708816</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1371,61 +1365,67 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>5460</v>
+        <v>8698.6</v>
       </c>
       <c r="V8">
-        <v>3.196908484103285</v>
+        <v>2.490580083605337</v>
       </c>
       <c r="W8">
-        <v>0.05103731166679814</v>
+        <v>0.08020855653167631</v>
       </c>
       <c r="X8">
-        <v>0.1721661317230974</v>
+        <v>0.09208043170724056</v>
       </c>
       <c r="Y8">
-        <v>-0.1211288200562992</v>
+        <v>-0.01187187517556425</v>
       </c>
       <c r="Z8">
-        <v>0.06553549416285984</v>
+        <v>0.09045577507789158</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.010861034893573e-05</v>
       </c>
       <c r="AB8">
-        <v>0.05685202483642058</v>
+        <v>0.0504795179777992</v>
       </c>
       <c r="AC8">
-        <v>-0.05685202483642058</v>
+        <v>-0.05045940936745027</v>
       </c>
       <c r="AD8">
-        <v>10901.4</v>
+        <v>12094.7</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>0.3486098295951212</v>
       </c>
       <c r="AF8">
-        <v>10901.4</v>
+        <v>12095.0486098296</v>
       </c>
       <c r="AG8">
-        <v>5441.4</v>
+        <v>3396.448609829595</v>
       </c>
       <c r="AH8">
-        <v>0.8645523542147463</v>
+        <v>0.7759379822176925</v>
       </c>
       <c r="AI8">
-        <v>0.8162724352494554</v>
+        <v>0.7951541300989967</v>
       </c>
       <c r="AJ8">
-        <v>0.7611094792497168</v>
+        <v>0.4930214318684576</v>
       </c>
       <c r="AK8">
-        <v>0.6892122962343732</v>
+        <v>0.5215397413926937</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
         <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>53046.9298245614</v>
+      </c>
+      <c r="AP8">
+        <v>14896.70442907717</v>
       </c>
     </row>
     <row r="9">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Berner Kantonalbank AG (SWX:BEKN)</t>
+          <t>Walliser Kantonalbank (SWX:WKBN)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0134</v>
+        <v>0.0275</v>
       </c>
       <c r="E9">
-        <v>0.0375</v>
+        <v>0.0538</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1457,97 +1457,100 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>-0.000137215851810007</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>-0.0001145885464409847</v>
       </c>
       <c r="K9">
-        <v>164.7</v>
+        <v>94.8</v>
       </c>
       <c r="L9">
-        <v>0.3313216656608328</v>
+        <v>0.3114323258869908</v>
       </c>
       <c r="M9">
-        <v>88.98120000000002</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.04003473409520383</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.5402622950819673</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>88.98120000000002</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.04003473409520383</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.5402622950819673</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>8531.299999999999</v>
+        <v>3449.4</v>
       </c>
       <c r="V9">
-        <v>3.838432466480698</v>
+        <v>1.699044429120284</v>
       </c>
       <c r="W9">
-        <v>0.05784630514189379</v>
+        <v>0.06312845441832589</v>
       </c>
       <c r="X9">
-        <v>0.1402326970431804</v>
+        <v>0.09136668003168683</v>
       </c>
       <c r="Y9">
-        <v>-0.08238639190128658</v>
+        <v>-0.02823822561336094</v>
       </c>
       <c r="Z9">
-        <v>0.1690183944782564</v>
+        <v>0.06263047360542116</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>-7.176734933355667e-06</v>
       </c>
       <c r="AB9">
-        <v>0.05702333187053502</v>
+        <v>0.05048678373674157</v>
       </c>
       <c r="AC9">
-        <v>-0.05702333187053502</v>
+        <v>-0.05049396047167493</v>
       </c>
       <c r="AD9">
-        <v>10140.8</v>
+        <v>6904.3</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>0.3538425264548306</v>
       </c>
       <c r="AF9">
-        <v>10140.8</v>
+        <v>6904.653842526455</v>
       </c>
       <c r="AG9">
-        <v>1609.5</v>
+        <v>3455.253842526455</v>
       </c>
       <c r="AH9">
-        <v>0.8202274455246938</v>
+        <v>0.7727774806637538</v>
       </c>
       <c r="AI9">
-        <v>0.7823423673633131</v>
+        <v>0.8049583218542151</v>
       </c>
       <c r="AJ9">
-        <v>0.4200046971634352</v>
+        <v>0.6298938869450146</v>
       </c>
       <c r="AK9">
-        <v>0.3632526857452379</v>
+        <v>0.6737680989723024</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
         <v>0</v>
+      </c>
+      <c r="AN9">
+        <v>238079.3103448276</v>
+      </c>
+      <c r="AP9">
+        <v>119146.6842250502</v>
       </c>
     </row>
     <row r="10">
@@ -1558,7 +1561,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Thurgauer Kantonalbank (SWX:TKBP)</t>
+          <t>Hypothekarbank Lenzburg AG (SWX:HBLN)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1567,10 +1570,10 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0197</v>
+        <v>0.0464</v>
       </c>
       <c r="E10">
-        <v>0.0223</v>
+        <v>-0.0204</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1585,85 +1588,82 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>153.5</v>
+        <v>21.9</v>
       </c>
       <c r="L10">
-        <v>0.3963335915311128</v>
+        <v>0.2005494505494505</v>
       </c>
       <c r="M10">
-        <v>65</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.02525350635222813</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>0.4234527687296417</v>
+        <v>-0</v>
       </c>
       <c r="P10">
-        <v>65</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.02525350635222813</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>0.4234527687296417</v>
+        <v>-0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>5682.4</v>
+        <v>1220.5</v>
       </c>
       <c r="V10">
-        <v>2.207700376860018</v>
+        <v>3.485151342090234</v>
       </c>
       <c r="W10">
-        <v>0.05985572236303373</v>
+        <v>0.03861071932299012</v>
       </c>
       <c r="X10">
-        <v>0.1322180461917942</v>
+        <v>0.08920895886577285</v>
       </c>
       <c r="Y10">
-        <v>-0.0723623238287605</v>
+        <v>-0.05059823954278272</v>
       </c>
       <c r="Z10">
-        <v>0.05627560954345993</v>
+        <v>0.2511499540018398</v>
       </c>
       <c r="AA10">
         <v>0</v>
       </c>
       <c r="AB10">
-        <v>0.05708550262472295</v>
+        <v>0.05051005060074121</v>
       </c>
       <c r="AC10">
-        <v>-0.05708550262472295</v>
+        <v>-0.05051005060074121</v>
       </c>
       <c r="AD10">
-        <v>10567.7</v>
+        <v>1125.3</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>10567.7</v>
+        <v>1125.3</v>
       </c>
       <c r="AG10">
-        <v>4885.300000000001</v>
+        <v>-95.20000000000005</v>
       </c>
       <c r="AH10">
-        <v>0.8041410482741828</v>
+        <v>0.7626567265333785</v>
       </c>
       <c r="AI10">
-        <v>0.8031021537245604</v>
+        <v>0.6432858857828846</v>
       </c>
       <c r="AJ10">
-        <v>0.6549361861861863</v>
+        <v>-0.3733333333333336</v>
       </c>
       <c r="AK10">
-        <v>0.6534469382841551</v>
+        <v>-0.1800302571860818</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>St. Galler Kantonalbank AG (SWX:SGKN)</t>
+          <t>Zuger Kantonalbank (SWX:ZUGER)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.0249</v>
+        <v>0.0649</v>
       </c>
       <c r="E11">
-        <v>0.0318</v>
+        <v>0.0866</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1701,34 +1701,34 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0.0002196390522287437</v>
+        <v>0</v>
       </c>
       <c r="J11">
-        <v>0.0001854818036000422</v>
+        <v>0</v>
       </c>
       <c r="K11">
-        <v>186.9</v>
+        <v>120.2</v>
       </c>
       <c r="L11">
-        <v>0.3483041371598956</v>
+        <v>0.384763124199744</v>
       </c>
       <c r="M11">
-        <v>106.444</v>
+        <v>70.79039999999999</v>
       </c>
       <c r="N11">
-        <v>0.03422086481273108</v>
+        <v>0.02738400835557618</v>
       </c>
       <c r="O11">
-        <v>0.5695238095238095</v>
+        <v>0.5889384359400998</v>
       </c>
       <c r="P11">
-        <v>106.444</v>
+        <v>70.79039999999999</v>
       </c>
       <c r="Q11">
-        <v>0.03422086481273108</v>
+        <v>0.02738400835557618</v>
       </c>
       <c r="R11">
-        <v>0.5695238095238095</v>
+        <v>0.5889384359400998</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1737,67 +1737,61 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>8243.700000000001</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>2.65028130525639</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>0.0667142602177405</v>
+        <v>0.08270831899814217</v>
       </c>
       <c r="X11">
-        <v>0.1282824023083361</v>
+        <v>0.07348010323261964</v>
       </c>
       <c r="Y11">
-        <v>-0.06156814209059557</v>
+        <v>0.009228215765522532</v>
       </c>
       <c r="Z11">
-        <v>0.08963904435640642</v>
+        <v>0.03825665266535225</v>
       </c>
       <c r="AA11">
-        <v>1.662641162021044e-05</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.05712029247107531</v>
+        <v>0.05068930899655288</v>
       </c>
       <c r="AC11">
-        <v>-0.0571036660594551</v>
+        <v>-0.05068930899655288</v>
       </c>
       <c r="AD11">
-        <v>12072.7</v>
+        <v>4770.3</v>
       </c>
       <c r="AE11">
-        <v>0.2907084228702805</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>12072.99070842287</v>
+        <v>4770.3</v>
       </c>
       <c r="AG11">
-        <v>3829.29070842287</v>
+        <v>4770.3</v>
       </c>
       <c r="AH11">
-        <v>0.7951393352337296</v>
+        <v>0.6485439269108411</v>
       </c>
       <c r="AI11">
-        <v>0.8117283604509817</v>
+        <v>0.748810925359077</v>
       </c>
       <c r="AJ11">
-        <v>0.5517876358685045</v>
+        <v>0.6485439269108411</v>
       </c>
       <c r="AK11">
-        <v>0.5776146127722447</v>
+        <v>0.748810925359077</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
         <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>68594.88636363637</v>
-      </c>
-      <c r="AP11">
-        <v>21757.33357058449</v>
       </c>
     </row>
     <row r="12">
@@ -1808,7 +1802,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Walliser Kantonalbank (SWX:WKBN)</t>
+          <t>Graubündner Kantonalbank (SWX:GRKP)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1817,10 +1811,10 @@
         </is>
       </c>
       <c r="D12">
-        <v>0.0104</v>
+        <v>0.0552</v>
       </c>
       <c r="E12">
-        <v>-0.0185</v>
+        <v>0.0346</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1829,16 +1823,16 @@
         <v>0</v>
       </c>
       <c r="I12">
-        <v>-0.0001210895825716041</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>-9.976906916170537e-05</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>72.90000000000001</v>
+        <v>236.3</v>
       </c>
       <c r="L12">
-        <v>0.2796317606444189</v>
+        <v>0.4230975828111012</v>
       </c>
       <c r="M12">
         <v>-0</v>
@@ -1862,67 +1856,61 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>3467.3</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>1.962474530224134</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>0.04863566615518047</v>
+        <v>0.08297050561797753</v>
       </c>
       <c r="X12">
-        <v>0.1279680939373795</v>
+        <v>0.07286843247180019</v>
       </c>
       <c r="Y12">
-        <v>-0.07933242778219904</v>
+        <v>0.01010207314617734</v>
       </c>
       <c r="Z12">
-        <v>0.06099611298783267</v>
+        <v>0.1153877938928144</v>
       </c>
       <c r="AA12">
-        <v>-6.085525415278273e-06</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.0571232092587371</v>
+        <v>0.05078778216705468</v>
       </c>
       <c r="AC12">
-        <v>-0.05712929478415237</v>
+        <v>-0.05078778216705468</v>
       </c>
       <c r="AD12">
-        <v>6825.5</v>
+        <v>9017.700000000001</v>
       </c>
       <c r="AE12">
-        <v>0.4428402708820859</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>6825.942840270882</v>
+        <v>9017.700000000001</v>
       </c>
       <c r="AG12">
-        <v>3358.642840270882</v>
+        <v>9017.700000000001</v>
       </c>
       <c r="AH12">
-        <v>0.7943846298157921</v>
+        <v>0.6418474547318074</v>
       </c>
       <c r="AI12">
-        <v>0.8196728619606418</v>
+        <v>0.7390830410123594</v>
       </c>
       <c r="AJ12">
-        <v>0.6552883223829643</v>
+        <v>0.6418474547318074</v>
       </c>
       <c r="AK12">
-        <v>0.691030026203603</v>
+        <v>0.7390830410123594</v>
       </c>
       <c r="AL12">
         <v>0</v>
       </c>
       <c r="AM12">
         <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>119745.6140350877</v>
-      </c>
-      <c r="AP12">
-        <v>58923.55860124354</v>
       </c>
     </row>
     <row r="13">
@@ -1933,7 +1921,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Graubündner Kantonalbank (SWX:GRKP)</t>
+          <t>Banque Cantonale Vaudoise (SWX:BCVN)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1942,10 +1930,10 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.0373</v>
+        <v>0.0264</v>
       </c>
       <c r="E13">
-        <v>0.00873</v>
+        <v>0.0464</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1960,28 +1948,28 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>190.5</v>
+        <v>482.2</v>
       </c>
       <c r="L13">
-        <v>0.4110919292188174</v>
+        <v>0.3934078485763237</v>
       </c>
       <c r="M13">
-        <v>110.805</v>
+        <v>365.075</v>
       </c>
       <c r="N13">
-        <v>0.02425360066541172</v>
+        <v>0.03299069221037412</v>
       </c>
       <c r="O13">
-        <v>0.5816535433070866</v>
+        <v>0.7571028618830362</v>
       </c>
       <c r="P13">
-        <v>110.805</v>
+        <v>365.075</v>
       </c>
       <c r="Q13">
-        <v>0.02425360066541172</v>
+        <v>0.03299069221037412</v>
       </c>
       <c r="R13">
-        <v>0.5816535433070866</v>
+        <v>0.7571028618830362</v>
       </c>
       <c r="S13">
         <v>0</v>
@@ -1990,55 +1978,55 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>8799.700000000001</v>
+        <v>14329.6</v>
       </c>
       <c r="V13">
-        <v>1.926126165564943</v>
+        <v>1.294921380806073</v>
       </c>
       <c r="W13">
-        <v>0.06544142906217795</v>
+        <v>0.1305854953149542</v>
       </c>
       <c r="X13">
-        <v>0.1016790178200009</v>
+        <v>0.07186594390294432</v>
       </c>
       <c r="Y13">
-        <v>-0.03623758875782299</v>
+        <v>0.05871955141200991</v>
       </c>
       <c r="Z13">
-        <v>0.03263242398208526</v>
+        <v>0.1575854975572127</v>
       </c>
       <c r="AA13">
         <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.05747712395431227</v>
+        <v>0.05081432259527011</v>
       </c>
       <c r="AC13">
-        <v>-0.05747712395431227</v>
+        <v>-0.05081432259527011</v>
       </c>
       <c r="AD13">
-        <v>10804.1</v>
+        <v>18866.6</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>10804.1</v>
+        <v>18866.6</v>
       </c>
       <c r="AG13">
-        <v>2004.4</v>
+        <v>4536.999999999998</v>
       </c>
       <c r="AH13">
-        <v>0.7028108269855002</v>
+        <v>0.6303027468378958</v>
       </c>
       <c r="AI13">
-        <v>0.7887355818367645</v>
+        <v>0.8230782654218654</v>
       </c>
       <c r="AJ13">
-        <v>0.3049444698006998</v>
+        <v>0.2907774145997564</v>
       </c>
       <c r="AK13">
-        <v>0.4092031929444909</v>
+        <v>0.5280247660723429</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2055,7 +2043,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Banque Cantonale Vaudoise (SWX:BCVN)</t>
+          <t>Banque Cantonale de Genève SA (SWX:BCGE)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2064,10 +2052,10 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0134</v>
+        <v>0.0728</v>
       </c>
       <c r="E14">
-        <v>0.049</v>
+        <v>0.199</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2082,28 +2070,28 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>421.2</v>
+        <v>239.6</v>
       </c>
       <c r="L14">
-        <v>0.3880239520958084</v>
+        <v>0.4020134228187919</v>
       </c>
       <c r="M14">
-        <v>332.433</v>
+        <v>43.788</v>
       </c>
       <c r="N14">
-        <v>0.04033499963600185</v>
+        <v>0.02302813568235604</v>
       </c>
       <c r="O14">
-        <v>0.7892521367521369</v>
+        <v>0.182754590984975</v>
       </c>
       <c r="P14">
-        <v>332.433</v>
+        <v>43.788</v>
       </c>
       <c r="Q14">
-        <v>0.04033499963600185</v>
+        <v>0.02302813568235604</v>
       </c>
       <c r="R14">
-        <v>0.7892521367521369</v>
+        <v>0.182754590984975</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2112,55 +2100,55 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>13533.6</v>
+        <v>7894.5</v>
       </c>
       <c r="V14">
-        <v>1.642068480186367</v>
+        <v>4.151722324480673</v>
       </c>
       <c r="W14">
-        <v>0.1132014620511718</v>
+        <v>0.1224385507690735</v>
       </c>
       <c r="X14">
-        <v>0.09769512371786335</v>
+        <v>0.1029215225859095</v>
       </c>
       <c r="Y14">
-        <v>0.01550633833330843</v>
+        <v>0.01951702818316398</v>
       </c>
       <c r="Z14">
-        <v>0.1568841124304825</v>
+        <v>0.05929109340336845</v>
       </c>
       <c r="AA14">
         <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.05756025353654513</v>
+        <v>0.05142814537114102</v>
       </c>
       <c r="AC14">
-        <v>-0.05756025353654513</v>
+        <v>-0.05142814537114102</v>
       </c>
       <c r="AD14">
-        <v>17619</v>
+        <v>8377.9</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>17619</v>
+        <v>8377.9</v>
       </c>
       <c r="AG14">
-        <v>4085.4</v>
+        <v>483.3999999999996</v>
       </c>
       <c r="AH14">
-        <v>0.6813014291901256</v>
+        <v>0.8150183862871374</v>
       </c>
       <c r="AI14">
-        <v>0.8267328591002084</v>
+        <v>0.7846165372692621</v>
       </c>
       <c r="AJ14">
-        <v>0.3314134596664287</v>
+        <v>0.2026919367688371</v>
       </c>
       <c r="AK14">
-        <v>0.5252507071226535</v>
+        <v>0.1736849669445242</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2177,7 +2165,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Banque Cantonale de Genève SA (SWX:BCGE)</t>
+          <t>Thurgauer Kantonalbank (SWX:TKBP)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2186,10 +2174,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0505</v>
+        <v>0.0261</v>
       </c>
       <c r="E15">
-        <v>0.108</v>
+        <v>0.0327</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2204,85 +2192,82 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>145.8</v>
+        <v>171.1</v>
       </c>
       <c r="L15">
-        <v>0.3000617410989916</v>
+        <v>0.3914436055822466</v>
       </c>
       <c r="M15">
-        <v>33.3468</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.02426457105435495</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>0.228716049382716</v>
+        <v>-0</v>
       </c>
       <c r="P15">
-        <v>33.3468</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.02426457105435495</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>0.228716049382716</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>0</v>
+        <v>5835.9</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>2.056125145333474</v>
       </c>
       <c r="W15">
-        <v>0.07685009487666035</v>
+        <v>0.06603882820641475</v>
       </c>
       <c r="X15">
-        <v>0.1635262616520862</v>
+        <v>0.1026282890583641</v>
       </c>
       <c r="Y15">
-        <v>-0.08667616677542582</v>
+        <v>-0.03658946085194936</v>
       </c>
       <c r="Z15">
-        <v>0.04461181705427409</v>
+        <v>0.05846553061715844</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.05822133060757824</v>
+        <v>0.05628833410399605</v>
       </c>
       <c r="AC15">
-        <v>-0.05822133060757824</v>
+        <v>-0.05628833410399605</v>
       </c>
       <c r="AD15">
-        <v>8095.2</v>
+        <v>12433</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>8095.2</v>
+        <v>12433</v>
       </c>
       <c r="AG15">
-        <v>8095.2</v>
+        <v>6597.1</v>
       </c>
       <c r="AH15">
-        <v>0.8548709013147473</v>
+        <v>0.8141415596576586</v>
       </c>
       <c r="AI15">
-        <v>0.8052842050812724</v>
+        <v>0.8106222616315459</v>
       </c>
       <c r="AJ15">
-        <v>0.8548709013147473</v>
+        <v>0.6991860440468872</v>
       </c>
       <c r="AK15">
-        <v>0.8052842050812724</v>
+        <v>0.6943073344769883</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/research/traditional_assets/database/data/switzerland/switzerland_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ15"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0491</v>
+        <v>0.0524</v>
       </c>
       <c r="E2">
-        <v>0.0408</v>
+        <v>0.0553</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +600,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>1.955678200419801e-05</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>1.672861819999401e-05</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>2129.9</v>
+        <v>1690.1</v>
       </c>
       <c r="L2">
-        <v>0.3575157364666387</v>
+        <v>0.3982140332689317</v>
       </c>
       <c r="M2">
-        <v>778.7814000000001</v>
+        <v>533.5133</v>
       </c>
       <c r="N2">
-        <v>0.02137178407067018</v>
+        <v>0.02303249940639368</v>
       </c>
       <c r="O2">
-        <v>0.3656422367247289</v>
+        <v>0.3156696645168925</v>
       </c>
       <c r="P2">
-        <v>778.7814000000001</v>
+        <v>533.5133</v>
       </c>
       <c r="Q2">
-        <v>0.02137178407067018</v>
+        <v>0.02303249940639368</v>
       </c>
       <c r="R2">
-        <v>0.3656422367247289</v>
+        <v>0.3156696645168925</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,67 +636,61 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>66499.89999999999</v>
+        <v>43221.7</v>
       </c>
       <c r="V2">
-        <v>1.824929952771291</v>
+        <v>1.865939948626071</v>
       </c>
       <c r="W2">
-        <v>0.0670258391521639</v>
+        <v>0.08313028981790203</v>
       </c>
       <c r="X2">
-        <v>0.09799984411196272</v>
+        <v>0.1112419599028084</v>
       </c>
       <c r="Y2">
-        <v>-0.03097400495979882</v>
+        <v>-0.02811167008490641</v>
       </c>
       <c r="Z2">
-        <v>0.08121673650798619</v>
+        <v>0.05910867922142329</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05048678373674157</v>
+        <v>0.05585093040753479</v>
       </c>
       <c r="AC2">
-        <v>-0.05049396047167493</v>
+        <v>-0.05585093040753479</v>
       </c>
       <c r="AD2">
-        <v>112369.1</v>
+        <v>91732.60000000001</v>
       </c>
       <c r="AE2">
-        <v>0.7024523560499518</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>112369.802452356</v>
+        <v>91732.60000000001</v>
       </c>
       <c r="AG2">
-        <v>45869.90245235605</v>
+        <v>48510.90000000001</v>
       </c>
       <c r="AH2">
-        <v>0.7551251808555249</v>
+        <v>0.7983961161431937</v>
       </c>
       <c r="AI2">
-        <v>0.793901708516152</v>
+        <v>0.8218772818700247</v>
       </c>
       <c r="AJ2">
-        <v>0.5572849471470513</v>
+        <v>0.6768232451195965</v>
       </c>
       <c r="AK2">
-        <v>0.6112620777268489</v>
+        <v>0.7093087182966379</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
-      </c>
-      <c r="AN2">
-        <v>437233.8521400779</v>
-      </c>
-      <c r="AP2">
-        <v>178482.1107095566</v>
       </c>
     </row>
     <row r="3">
@@ -707,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glarner Kantonalbank (SWX:GLKBN)</t>
+          <t>Luzerner Kantonalbank AG (SWX:LUKN)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -716,10 +710,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0649</v>
+        <v>0.0524</v>
       </c>
       <c r="E3">
-        <v>0.0486</v>
+        <v>0.0667</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,10 +728,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>29.8</v>
+        <v>335.5</v>
       </c>
       <c r="L3">
-        <v>0.2687105500450856</v>
+        <v>0.4397693013501114</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -761,55 +755,55 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1767.8</v>
+        <v>10582.1</v>
       </c>
       <c r="V3">
-        <v>4.815581585399073</v>
+        <v>3.043281950995054</v>
       </c>
       <c r="W3">
-        <v>0.07088487155090391</v>
+        <v>0.08273736128236744</v>
       </c>
       <c r="X3">
-        <v>0.1795209841974771</v>
+        <v>0.1531179770034752</v>
       </c>
       <c r="Y3">
-        <v>-0.1086361126465731</v>
+        <v>-0.07038061572110771</v>
       </c>
       <c r="Z3">
-        <v>0.04960193219429287</v>
+        <v>0.02370682958055475</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05015491207103377</v>
+        <v>0.05480453851963311</v>
       </c>
       <c r="AC3">
-        <v>-0.05015491207103377</v>
+        <v>-0.05480453851963311</v>
       </c>
       <c r="AD3">
-        <v>4063.1</v>
+        <v>30385.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>4063.1</v>
+        <v>30385.7</v>
       </c>
       <c r="AG3">
-        <v>2295.3</v>
+        <v>19803.6</v>
       </c>
       <c r="AH3">
-        <v>0.9171369238409102</v>
+        <v>0.8973153510183711</v>
       </c>
       <c r="AI3">
-        <v>0.8979424959667618</v>
+        <v>0.8659114872759397</v>
       </c>
       <c r="AJ3">
-        <v>0.8621168870192308</v>
+        <v>0.8506408714477165</v>
       </c>
       <c r="AK3">
-        <v>0.8325051684741214</v>
+        <v>0.8080166796551457</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -826,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Banque Cantonale du Jura SA (SWX:BCJ)</t>
+          <t>Basellandschaftliche Kantonalbank (SWX:BLKB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,10 +829,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0508</v>
+        <v>0.0563</v>
       </c>
       <c r="E4">
-        <v>0.0337</v>
+        <v>0.0295</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -853,10 +847,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>13</v>
+        <v>174</v>
       </c>
       <c r="L4">
-        <v>0.1943198804185351</v>
+        <v>0.3350019252984213</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -880,55 +874,55 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>916.6</v>
+        <v>6432.4</v>
       </c>
       <c r="V4">
-        <v>4.773958333333334</v>
+        <v>3.136379150616802</v>
       </c>
       <c r="W4">
-        <v>0.04359490274983233</v>
+        <v>0.05668675680078188</v>
       </c>
       <c r="X4">
-        <v>0.1479816444461206</v>
+        <v>0.1184218750689963</v>
       </c>
       <c r="Y4">
-        <v>-0.1043867416962882</v>
+        <v>-0.06173511826821438</v>
       </c>
       <c r="Z4">
-        <v>0.07274111123192345</v>
+        <v>0.07344114315932655</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05021094960816305</v>
+        <v>0.05501081492434111</v>
       </c>
       <c r="AC4">
-        <v>-0.05021094960816305</v>
+        <v>-0.05501081492434111</v>
       </c>
       <c r="AD4">
-        <v>1598.4</v>
+        <v>11351.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1598.4</v>
+        <v>11351.3</v>
       </c>
       <c r="AG4">
-        <v>681.8000000000001</v>
+        <v>4918.9</v>
       </c>
       <c r="AH4">
-        <v>0.8927613941018767</v>
+        <v>0.8469728850487234</v>
       </c>
       <c r="AI4">
-        <v>0.8303376623376624</v>
+        <v>0.7815708118454664</v>
       </c>
       <c r="AJ4">
-        <v>0.7802700846875715</v>
+        <v>0.705744784642314</v>
       </c>
       <c r="AK4">
-        <v>0.6761205870686235</v>
+        <v>0.6079245609481789</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -945,7 +939,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Basellandschaftliche Kantonalbank (SWX:BLKB)</t>
+          <t>Glarner Kantonalbank (SWX:GLKBN)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -954,10 +948,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0321</v>
+        <v>0.0435</v>
       </c>
       <c r="E5">
-        <v>0.0118</v>
+        <v>0.00127</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -972,10 +966,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>157.8</v>
+        <v>27.9</v>
       </c>
       <c r="L5">
-        <v>0.3320707070707071</v>
+        <v>0.2595348837209302</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -999,55 +993,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>6737.8</v>
+        <v>1728.1</v>
       </c>
       <c r="V5">
-        <v>3.062497159220036</v>
+        <v>5.52285075103867</v>
       </c>
       <c r="W5">
-        <v>0.05692640692640693</v>
+        <v>0.06041576440017323</v>
       </c>
       <c r="X5">
-        <v>0.1084066428509598</v>
+        <v>0.204937837520551</v>
       </c>
       <c r="Y5">
-        <v>-0.05148023592455291</v>
+        <v>-0.1445220731203778</v>
       </c>
       <c r="Z5">
-        <v>0.06223479490806223</v>
+        <v>0.03899024337165864</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05024886465051894</v>
+        <v>0.05530207753722832</v>
       </c>
       <c r="AC5">
-        <v>-0.05024886465051894</v>
+        <v>-0.05530207753722832</v>
       </c>
       <c r="AD5">
-        <v>10743.1</v>
+        <v>4231.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>10743.1</v>
+        <v>4231.5</v>
       </c>
       <c r="AG5">
-        <v>4005.3</v>
+        <v>2503.4</v>
       </c>
       <c r="AH5">
-        <v>0.8300188515977501</v>
+        <v>0.9311460258780038</v>
       </c>
       <c r="AI5">
-        <v>0.7777753645222478</v>
+        <v>0.8995726949977679</v>
       </c>
       <c r="AJ5">
-        <v>0.6454539594546685</v>
+        <v>0.8888967794624152</v>
       </c>
       <c r="AK5">
-        <v>0.5661361451913836</v>
+        <v>0.8412527723637341</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1064,7 +1058,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Valiant Holding AG (SWX:VATN)</t>
+          <t>Zuger Kantonalbank (SWX:ZUGER)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1073,10 +1067,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0491</v>
+        <v>0.0848</v>
       </c>
       <c r="E6">
-        <v>0.0254</v>
+        <v>0.09390000000000001</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1091,28 +1085,28 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>149.5</v>
+        <v>135.9</v>
       </c>
       <c r="L6">
-        <v>0.2603169075396135</v>
+        <v>0.3976009362200117</v>
       </c>
       <c r="M6">
-        <v>86.426</v>
+        <v>70.50239999999999</v>
       </c>
       <c r="N6">
-        <v>0.04830427006483345</v>
+        <v>0.02695870296726828</v>
       </c>
       <c r="O6">
-        <v>0.5781003344481606</v>
+        <v>0.5187814569536423</v>
       </c>
       <c r="P6">
-        <v>86.426</v>
+        <v>70.50239999999999</v>
       </c>
       <c r="Q6">
-        <v>0.04830427006483345</v>
+        <v>0.02695870296726828</v>
       </c>
       <c r="R6">
-        <v>0.5781003344481606</v>
+        <v>0.5187814569536423</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1121,55 +1115,55 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>6108.5</v>
+        <v>2780.6</v>
       </c>
       <c r="V6">
-        <v>3.414095685222446</v>
+        <v>1.063245640868767</v>
       </c>
       <c r="W6">
-        <v>0.06092839385417941</v>
+        <v>0.08492688413948257</v>
       </c>
       <c r="X6">
-        <v>0.1296992699514897</v>
+        <v>0.077897193755947</v>
       </c>
       <c r="Y6">
-        <v>-0.06877087609731032</v>
+        <v>0.00702969038353557</v>
       </c>
       <c r="Z6">
-        <v>0.07274132056592064</v>
+        <v>0.05412595607214683</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05026163032591283</v>
+        <v>0.05585093040753479</v>
       </c>
       <c r="AC6">
-        <v>-0.05026163032591283</v>
+        <v>-0.05585093040753479</v>
       </c>
       <c r="AD6">
-        <v>12050.1</v>
+        <v>4688.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>12050.1</v>
+        <v>4688.6</v>
       </c>
       <c r="AG6">
-        <v>5941.6</v>
+        <v>1908</v>
       </c>
       <c r="AH6">
-        <v>0.870716004422189</v>
+        <v>0.6419398121525781</v>
       </c>
       <c r="AI6">
-        <v>0.81371761194433</v>
+        <v>0.7387228410720194</v>
       </c>
       <c r="AJ6">
-        <v>0.768562115175661</v>
+        <v>0.4218252564556067</v>
       </c>
       <c r="AK6">
-        <v>0.6829268292682926</v>
+        <v>0.5350082718784175</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1186,7 +1180,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Berner Kantonalbank AG (SWX:BEKN)</t>
+          <t>Banque Cantonale Vaudoise (SWX:BCVN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1195,10 +1189,10 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.06309999999999999</v>
+        <v>0.0331</v>
       </c>
       <c r="E7">
-        <v>0.0408</v>
+        <v>0.055</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1213,28 +1207,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>189.1</v>
+        <v>501.1</v>
       </c>
       <c r="L7">
-        <v>0.3219819513025711</v>
+        <v>0.3884496124031008</v>
       </c>
       <c r="M7">
-        <v>99.08199999999999</v>
+        <v>411.461</v>
       </c>
       <c r="N7">
-        <v>0.03817453284530919</v>
+        <v>0.05199022011068712</v>
       </c>
       <c r="O7">
-        <v>0.5239661554732945</v>
+        <v>0.8211155457992416</v>
       </c>
       <c r="P7">
-        <v>99.08199999999999</v>
+        <v>411.461</v>
       </c>
       <c r="Q7">
-        <v>0.03817453284530919</v>
+        <v>0.05199022011068712</v>
       </c>
       <c r="R7">
-        <v>0.5239661554732945</v>
+        <v>0.8211155457992416</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1243,55 +1237,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>9540.700000000001</v>
+        <v>13981.7</v>
       </c>
       <c r="V7">
-        <v>3.675862068965518</v>
+        <v>1.766659927724849</v>
       </c>
       <c r="W7">
-        <v>0.0670258391521639</v>
+        <v>0.1235636435370124</v>
       </c>
       <c r="X7">
-        <v>0.09799984411196272</v>
+        <v>0.08830402978874489</v>
       </c>
       <c r="Y7">
-        <v>-0.03097400495979882</v>
+        <v>0.03525961374826748</v>
       </c>
       <c r="Z7">
-        <v>0.1325494267400921</v>
+        <v>0.1501326753875518</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05042624386450563</v>
+        <v>0.05597654732662422</v>
       </c>
       <c r="AC7">
-        <v>-0.05042624386450563</v>
+        <v>-0.05597654732662422</v>
       </c>
       <c r="AD7">
-        <v>10324.6</v>
+        <v>21793.9</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>10324.6</v>
+        <v>21793.9</v>
       </c>
       <c r="AG7">
-        <v>783.8999999999996</v>
+        <v>7812.200000000001</v>
       </c>
       <c r="AH7">
-        <v>0.7991114619855884</v>
+        <v>0.733601273726694</v>
       </c>
       <c r="AI7">
-        <v>0.7691665859600242</v>
+        <v>0.840839995061576</v>
       </c>
       <c r="AJ7">
-        <v>0.2319642540095874</v>
+        <v>0.4967570454776681</v>
       </c>
       <c r="AK7">
-        <v>0.2019111889552853</v>
+        <v>0.6544251308900524</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1308,7 +1302,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>St. Galler Kantonalbank AG (SWX:SGKN)</t>
+          <t>Graubündner Kantonalbank (SWX:GRKP)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1317,10 +1311,10 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0235</v>
+        <v>0.0449</v>
       </c>
       <c r="E8">
-        <v>0.0512</v>
+        <v>0.0553</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1329,103 +1323,94 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0.0002639727052718075</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>0.0002223032231122908</v>
+        <v>0</v>
       </c>
       <c r="K8">
-        <v>224.6</v>
+        <v>259.3</v>
       </c>
       <c r="L8">
-        <v>0.3745830553702468</v>
+        <v>0.4656132160172383</v>
       </c>
       <c r="M8">
-        <v>113.62</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.03253163832102159</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.5058771148708816</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>113.62</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.03253163832102159</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.5058771148708816</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>8698.6</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>2.490580083605337</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>0.08020855653167631</v>
+        <v>0.08313028981790203</v>
       </c>
       <c r="X8">
-        <v>0.09208043170724056</v>
+        <v>0.07998492846293345</v>
       </c>
       <c r="Y8">
-        <v>-0.01187187517556425</v>
+        <v>0.003145361354968582</v>
       </c>
       <c r="Z8">
-        <v>0.09045577507789158</v>
+        <v>0.04601414548699474</v>
       </c>
       <c r="AA8">
-        <v>2.010861034893573e-05</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>0.0504795179777992</v>
+        <v>0.05621056750817096</v>
       </c>
       <c r="AC8">
-        <v>-0.05045940936745027</v>
+        <v>-0.05621056750817096</v>
       </c>
       <c r="AD8">
-        <v>12094.7</v>
+        <v>9502.9</v>
       </c>
       <c r="AE8">
-        <v>0.3486098295951212</v>
+        <v>0</v>
       </c>
       <c r="AF8">
-        <v>12095.0486098296</v>
+        <v>9502.9</v>
       </c>
       <c r="AG8">
-        <v>3396.448609829595</v>
+        <v>9502.9</v>
       </c>
       <c r="AH8">
-        <v>0.7759379822176925</v>
+        <v>0.6650593471810089</v>
       </c>
       <c r="AI8">
-        <v>0.7951541300989967</v>
+        <v>0.7454541175732283</v>
       </c>
       <c r="AJ8">
-        <v>0.4930214318684576</v>
+        <v>0.6650593471810089</v>
       </c>
       <c r="AK8">
-        <v>0.5215397413926937</v>
+        <v>0.7454541175732283</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
         <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>53046.9298245614</v>
-      </c>
-      <c r="AP8">
-        <v>14896.70442907717</v>
       </c>
     </row>
     <row r="9">
@@ -1436,7 +1421,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Walliser Kantonalbank (SWX:WKBN)</t>
+          <t>Banque Cantonale de Genève SA (SWX:BCGE)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1445,10 +1430,10 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0275</v>
+        <v>0.06849999999999999</v>
       </c>
       <c r="E9">
-        <v>0.0538</v>
+        <v>0.186</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1457,822 +1442,96 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>-0.000137215851810007</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>-0.0001145885464409847</v>
+        <v>0</v>
       </c>
       <c r="K9">
-        <v>94.8</v>
+        <v>256.4</v>
       </c>
       <c r="L9">
-        <v>0.3114323258869908</v>
+        <v>0.3851584797957037</v>
       </c>
       <c r="M9">
-        <v>-0</v>
+        <v>51.5499</v>
       </c>
       <c r="N9">
-        <v>-0</v>
+        <v>0.02568249302510961</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0.2010526521060843</v>
       </c>
       <c r="P9">
-        <v>-0</v>
+        <v>51.5499</v>
       </c>
       <c r="Q9">
-        <v>-0</v>
+        <v>0.02568249302510961</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0.2010526521060843</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
       <c r="U9">
-        <v>3449.4</v>
+        <v>7716.8</v>
       </c>
       <c r="V9">
-        <v>1.699044429120284</v>
+        <v>3.844559585492228</v>
       </c>
       <c r="W9">
-        <v>0.06312845441832589</v>
+        <v>0.1114879554743891</v>
       </c>
       <c r="X9">
-        <v>0.09136668003168683</v>
+        <v>0.1112419599028084</v>
       </c>
       <c r="Y9">
-        <v>-0.02823822561336094</v>
+        <v>0.000245995571580615</v>
       </c>
       <c r="Z9">
-        <v>0.06263047360542116</v>
+        <v>0.2391851106639838</v>
       </c>
       <c r="AA9">
-        <v>-7.176734933355667e-06</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>0.05048678373674157</v>
+        <v>0.05635701807727175</v>
       </c>
       <c r="AC9">
-        <v>-0.05049396047167493</v>
+        <v>-0.05635701807727175</v>
       </c>
       <c r="AD9">
-        <v>6904.3</v>
+        <v>9778.700000000001</v>
       </c>
       <c r="AE9">
-        <v>0.3538425264548306</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>6904.653842526455</v>
+        <v>9778.700000000001</v>
       </c>
       <c r="AG9">
-        <v>3455.253842526455</v>
+        <v>2061.900000000001</v>
       </c>
       <c r="AH9">
-        <v>0.7727774806637538</v>
+        <v>0.8296948048091363</v>
       </c>
       <c r="AI9">
-        <v>0.8049583218542151</v>
+        <v>0.796246234020031</v>
       </c>
       <c r="AJ9">
-        <v>0.6298938869450146</v>
+        <v>0.5067213880219213</v>
       </c>
       <c r="AK9">
-        <v>0.6737680989723024</v>
+        <v>0.4517549625345078</v>
       </c>
       <c r="AL9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>0</v>
-      </c>
-      <c r="AN9">
-        <v>238079.3103448276</v>
-      </c>
-      <c r="AP9">
-        <v>119146.6842250502</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Hypothekarbank Lenzburg AG (SWX:HBLN)</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>0.0464</v>
-      </c>
-      <c r="E10">
-        <v>-0.0204</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>21.9</v>
-      </c>
-      <c r="L10">
-        <v>0.2005494505494505</v>
-      </c>
-      <c r="M10">
-        <v>-0</v>
-      </c>
-      <c r="N10">
-        <v>-0</v>
-      </c>
-      <c r="O10">
-        <v>-0</v>
-      </c>
-      <c r="P10">
-        <v>-0</v>
-      </c>
-      <c r="Q10">
-        <v>-0</v>
-      </c>
-      <c r="R10">
-        <v>-0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="U10">
-        <v>1220.5</v>
-      </c>
-      <c r="V10">
-        <v>3.485151342090234</v>
-      </c>
-      <c r="W10">
-        <v>0.03861071932299012</v>
-      </c>
-      <c r="X10">
-        <v>0.08920895886577285</v>
-      </c>
-      <c r="Y10">
-        <v>-0.05059823954278272</v>
-      </c>
-      <c r="Z10">
-        <v>0.2511499540018398</v>
-      </c>
-      <c r="AA10">
-        <v>0</v>
-      </c>
-      <c r="AB10">
-        <v>0.05051005060074121</v>
-      </c>
-      <c r="AC10">
-        <v>-0.05051005060074121</v>
-      </c>
-      <c r="AD10">
-        <v>1125.3</v>
-      </c>
-      <c r="AE10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>1125.3</v>
-      </c>
-      <c r="AG10">
-        <v>-95.20000000000005</v>
-      </c>
-      <c r="AH10">
-        <v>0.7626567265333785</v>
-      </c>
-      <c r="AI10">
-        <v>0.6432858857828846</v>
-      </c>
-      <c r="AJ10">
-        <v>-0.3733333333333336</v>
-      </c>
-      <c r="AK10">
-        <v>-0.1800302571860818</v>
-      </c>
-      <c r="AL10">
-        <v>0</v>
-      </c>
-      <c r="AM10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Zuger Kantonalbank (SWX:ZUGER)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>0.0649</v>
-      </c>
-      <c r="E11">
-        <v>0.0866</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>120.2</v>
-      </c>
-      <c r="L11">
-        <v>0.384763124199744</v>
-      </c>
-      <c r="M11">
-        <v>70.79039999999999</v>
-      </c>
-      <c r="N11">
-        <v>0.02738400835557618</v>
-      </c>
-      <c r="O11">
-        <v>0.5889384359400998</v>
-      </c>
-      <c r="P11">
-        <v>70.79039999999999</v>
-      </c>
-      <c r="Q11">
-        <v>0.02738400835557618</v>
-      </c>
-      <c r="R11">
-        <v>0.5889384359400998</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0.08270831899814217</v>
-      </c>
-      <c r="X11">
-        <v>0.07348010323261964</v>
-      </c>
-      <c r="Y11">
-        <v>0.009228215765522532</v>
-      </c>
-      <c r="Z11">
-        <v>0.03825665266535225</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.05068930899655288</v>
-      </c>
-      <c r="AC11">
-        <v>-0.05068930899655288</v>
-      </c>
-      <c r="AD11">
-        <v>4770.3</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>4770.3</v>
-      </c>
-      <c r="AG11">
-        <v>4770.3</v>
-      </c>
-      <c r="AH11">
-        <v>0.6485439269108411</v>
-      </c>
-      <c r="AI11">
-        <v>0.748810925359077</v>
-      </c>
-      <c r="AJ11">
-        <v>0.6485439269108411</v>
-      </c>
-      <c r="AK11">
-        <v>0.748810925359077</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Graubündner Kantonalbank (SWX:GRKP)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.0552</v>
-      </c>
-      <c r="E12">
-        <v>0.0346</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>236.3</v>
-      </c>
-      <c r="L12">
-        <v>0.4230975828111012</v>
-      </c>
-      <c r="M12">
-        <v>-0</v>
-      </c>
-      <c r="N12">
-        <v>-0</v>
-      </c>
-      <c r="O12">
-        <v>-0</v>
-      </c>
-      <c r="P12">
-        <v>-0</v>
-      </c>
-      <c r="Q12">
-        <v>-0</v>
-      </c>
-      <c r="R12">
-        <v>-0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>0</v>
-      </c>
-      <c r="V12">
-        <v>0</v>
-      </c>
-      <c r="W12">
-        <v>0.08297050561797753</v>
-      </c>
-      <c r="X12">
-        <v>0.07286843247180019</v>
-      </c>
-      <c r="Y12">
-        <v>0.01010207314617734</v>
-      </c>
-      <c r="Z12">
-        <v>0.1153877938928144</v>
-      </c>
-      <c r="AA12">
-        <v>0</v>
-      </c>
-      <c r="AB12">
-        <v>0.05078778216705468</v>
-      </c>
-      <c r="AC12">
-        <v>-0.05078778216705468</v>
-      </c>
-      <c r="AD12">
-        <v>9017.700000000001</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>9017.700000000001</v>
-      </c>
-      <c r="AG12">
-        <v>9017.700000000001</v>
-      </c>
-      <c r="AH12">
-        <v>0.6418474547318074</v>
-      </c>
-      <c r="AI12">
-        <v>0.7390830410123594</v>
-      </c>
-      <c r="AJ12">
-        <v>0.6418474547318074</v>
-      </c>
-      <c r="AK12">
-        <v>0.7390830410123594</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Banque Cantonale Vaudoise (SWX:BCVN)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.0264</v>
-      </c>
-      <c r="E13">
-        <v>0.0464</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>482.2</v>
-      </c>
-      <c r="L13">
-        <v>0.3934078485763237</v>
-      </c>
-      <c r="M13">
-        <v>365.075</v>
-      </c>
-      <c r="N13">
-        <v>0.03299069221037412</v>
-      </c>
-      <c r="O13">
-        <v>0.7571028618830362</v>
-      </c>
-      <c r="P13">
-        <v>365.075</v>
-      </c>
-      <c r="Q13">
-        <v>0.03299069221037412</v>
-      </c>
-      <c r="R13">
-        <v>0.7571028618830362</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>14329.6</v>
-      </c>
-      <c r="V13">
-        <v>1.294921380806073</v>
-      </c>
-      <c r="W13">
-        <v>0.1305854953149542</v>
-      </c>
-      <c r="X13">
-        <v>0.07186594390294432</v>
-      </c>
-      <c r="Y13">
-        <v>0.05871955141200991</v>
-      </c>
-      <c r="Z13">
-        <v>0.1575854975572127</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0.05081432259527011</v>
-      </c>
-      <c r="AC13">
-        <v>-0.05081432259527011</v>
-      </c>
-      <c r="AD13">
-        <v>18866.6</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>18866.6</v>
-      </c>
-      <c r="AG13">
-        <v>4536.999999999998</v>
-      </c>
-      <c r="AH13">
-        <v>0.6303027468378958</v>
-      </c>
-      <c r="AI13">
-        <v>0.8230782654218654</v>
-      </c>
-      <c r="AJ13">
-        <v>0.2907774145997564</v>
-      </c>
-      <c r="AK13">
-        <v>0.5280247660723429</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Banque Cantonale de Genève SA (SWX:BCGE)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>0.0728</v>
-      </c>
-      <c r="E14">
-        <v>0.199</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>239.6</v>
-      </c>
-      <c r="L14">
-        <v>0.4020134228187919</v>
-      </c>
-      <c r="M14">
-        <v>43.788</v>
-      </c>
-      <c r="N14">
-        <v>0.02302813568235604</v>
-      </c>
-      <c r="O14">
-        <v>0.182754590984975</v>
-      </c>
-      <c r="P14">
-        <v>43.788</v>
-      </c>
-      <c r="Q14">
-        <v>0.02302813568235604</v>
-      </c>
-      <c r="R14">
-        <v>0.182754590984975</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14">
-        <v>7894.5</v>
-      </c>
-      <c r="V14">
-        <v>4.151722324480673</v>
-      </c>
-      <c r="W14">
-        <v>0.1224385507690735</v>
-      </c>
-      <c r="X14">
-        <v>0.1029215225859095</v>
-      </c>
-      <c r="Y14">
-        <v>0.01951702818316398</v>
-      </c>
-      <c r="Z14">
-        <v>0.05929109340336845</v>
-      </c>
-      <c r="AA14">
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <v>0.05142814537114102</v>
-      </c>
-      <c r="AC14">
-        <v>-0.05142814537114102</v>
-      </c>
-      <c r="AD14">
-        <v>8377.9</v>
-      </c>
-      <c r="AE14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>8377.9</v>
-      </c>
-      <c r="AG14">
-        <v>483.3999999999996</v>
-      </c>
-      <c r="AH14">
-        <v>0.8150183862871374</v>
-      </c>
-      <c r="AI14">
-        <v>0.7846165372692621</v>
-      </c>
-      <c r="AJ14">
-        <v>0.2026919367688371</v>
-      </c>
-      <c r="AK14">
-        <v>0.1736849669445242</v>
-      </c>
-      <c r="AL14">
-        <v>0</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Switzerland</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Thurgauer Kantonalbank (SWX:TKBP)</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Banks (Regional)</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>0.0261</v>
-      </c>
-      <c r="E15">
-        <v>0.0327</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>171.1</v>
-      </c>
-      <c r="L15">
-        <v>0.3914436055822466</v>
-      </c>
-      <c r="M15">
-        <v>-0</v>
-      </c>
-      <c r="N15">
-        <v>-0</v>
-      </c>
-      <c r="O15">
-        <v>-0</v>
-      </c>
-      <c r="P15">
-        <v>-0</v>
-      </c>
-      <c r="Q15">
-        <v>-0</v>
-      </c>
-      <c r="R15">
-        <v>-0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="U15">
-        <v>5835.9</v>
-      </c>
-      <c r="V15">
-        <v>2.056125145333474</v>
-      </c>
-      <c r="W15">
-        <v>0.06603882820641475</v>
-      </c>
-      <c r="X15">
-        <v>0.1026282890583641</v>
-      </c>
-      <c r="Y15">
-        <v>-0.03658946085194936</v>
-      </c>
-      <c r="Z15">
-        <v>0.05846553061715844</v>
-      </c>
-      <c r="AA15">
-        <v>0</v>
-      </c>
-      <c r="AB15">
-        <v>0.05628833410399605</v>
-      </c>
-      <c r="AC15">
-        <v>-0.05628833410399605</v>
-      </c>
-      <c r="AD15">
-        <v>12433</v>
-      </c>
-      <c r="AE15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>12433</v>
-      </c>
-      <c r="AG15">
-        <v>6597.1</v>
-      </c>
-      <c r="AH15">
-        <v>0.8141415596576586</v>
-      </c>
-      <c r="AI15">
-        <v>0.8106222616315459</v>
-      </c>
-      <c r="AJ15">
-        <v>0.6991860440468872</v>
-      </c>
-      <c r="AK15">
-        <v>0.6943073344769883</v>
-      </c>
-      <c r="AL15">
-        <v>0</v>
-      </c>
-      <c r="AM15">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/switzerland/switzerland_banks_regional.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_banks_regional.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,13 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0524</v>
+        <v>0.05435</v>
       </c>
       <c r="E2">
-        <v>0.0553</v>
+        <v>0.04995</v>
+      </c>
+      <c r="F2">
+        <v>0.142</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -600,34 +603,34 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>2.221305518714501E-05</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1.894424987448037E-05</v>
       </c>
       <c r="K2">
-        <v>1690.1</v>
+        <v>2600.1</v>
       </c>
       <c r="L2">
-        <v>0.3982140332689317</v>
+        <v>0.3651415571284125</v>
       </c>
       <c r="M2">
-        <v>533.5133</v>
+        <v>938.4023000000001</v>
       </c>
       <c r="N2">
-        <v>0.02303249940639368</v>
+        <v>0.02643654849505865</v>
       </c>
       <c r="O2">
-        <v>0.3156696645168925</v>
+        <v>0.3609100803815238</v>
       </c>
       <c r="P2">
-        <v>533.5133</v>
+        <v>938.4023000000001</v>
       </c>
       <c r="Q2">
-        <v>0.02303249940639368</v>
+        <v>0.02643654849505865</v>
       </c>
       <c r="R2">
-        <v>0.3156696645168925</v>
+        <v>0.3609100803815238</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,61 +639,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>43221.7</v>
+        <v>76552.10000000001</v>
       </c>
       <c r="V2">
-        <v>1.865939948626071</v>
+        <v>2.156615882173967</v>
       </c>
       <c r="W2">
-        <v>0.08313028981790203</v>
+        <v>0.0634534966572359</v>
       </c>
       <c r="X2">
-        <v>0.1112419599028084</v>
+        <v>0.110278890894964</v>
       </c>
       <c r="Y2">
-        <v>-0.02811167008490641</v>
+        <v>-0.04682539423772811</v>
       </c>
       <c r="Z2">
-        <v>0.05910867922142329</v>
+        <v>0.06650892178681733</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05585093040753479</v>
+        <v>0.05576088051226989</v>
       </c>
       <c r="AC2">
-        <v>-0.05585093040753479</v>
+        <v>-0.05576088051226989</v>
       </c>
       <c r="AD2">
-        <v>91732.60000000001</v>
+        <v>153032.2</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>0.949126383116889</v>
       </c>
       <c r="AF2">
-        <v>91732.60000000001</v>
+        <v>153033.1491263831</v>
       </c>
       <c r="AG2">
-        <v>48510.90000000001</v>
+        <v>76481.04912638312</v>
       </c>
       <c r="AH2">
-        <v>0.7983961161431937</v>
+        <v>0.8117197003627026</v>
       </c>
       <c r="AI2">
-        <v>0.8218772818700247</v>
+        <v>0.8131637563575854</v>
       </c>
       <c r="AJ2">
-        <v>0.6768232451195965</v>
+        <v>0.6830040309282537</v>
       </c>
       <c r="AK2">
-        <v>0.7093087182966379</v>
+        <v>0.6850522602684219</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
         <v>0</v>
+      </c>
+      <c r="AN2">
+        <v>439747.7011494254</v>
+      </c>
+      <c r="AP2">
+        <v>219773.1296735147</v>
       </c>
     </row>
     <row r="3">
@@ -764,10 +773,10 @@
         <v>0.08273736128236744</v>
       </c>
       <c r="X3">
-        <v>0.1531179770034752</v>
+        <v>0.1530489810859602</v>
       </c>
       <c r="Y3">
-        <v>-0.07038061572110771</v>
+        <v>-0.0703116198035928</v>
       </c>
       <c r="Z3">
         <v>0.02370682958055475</v>
@@ -776,10 +785,10 @@
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05480453851963311</v>
+        <v>0.05479745369806192</v>
       </c>
       <c r="AC3">
-        <v>-0.05480453851963311</v>
+        <v>-0.05479745369806192</v>
       </c>
       <c r="AD3">
         <v>30385.7</v>
@@ -883,10 +892,10 @@
         <v>0.05668675680078188</v>
       </c>
       <c r="X4">
-        <v>0.1184218750689963</v>
+        <v>0.1183751856601764</v>
       </c>
       <c r="Y4">
-        <v>-0.06173511826821438</v>
+        <v>-0.0616884288593945</v>
       </c>
       <c r="Z4">
         <v>0.07344114315932655</v>
@@ -895,10 +904,10 @@
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.05501081492434111</v>
+        <v>0.05500367017881062</v>
       </c>
       <c r="AC4">
-        <v>-0.05501081492434111</v>
+        <v>-0.05500367017881062</v>
       </c>
       <c r="AD4">
         <v>11351.3</v>
@@ -1002,10 +1011,10 @@
         <v>0.06041576440017323</v>
       </c>
       <c r="X5">
-        <v>0.204937837520551</v>
+        <v>0.204835526040055</v>
       </c>
       <c r="Y5">
-        <v>-0.1445220731203778</v>
+        <v>-0.1444197616398817</v>
       </c>
       <c r="Z5">
         <v>0.03899024337165864</v>
@@ -1014,10 +1023,10 @@
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05530207753722832</v>
+        <v>0.05529503298519786</v>
       </c>
       <c r="AC5">
-        <v>-0.05530207753722832</v>
+        <v>-0.05529503298519786</v>
       </c>
       <c r="AD5">
         <v>4231.5</v>
@@ -1058,7 +1067,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Zuger Kantonalbank (SWX:ZUGER)</t>
+          <t>Banque Cantonale du Jura SA (SWX:BCJ)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1067,10 +1076,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0848</v>
+        <v>0.104</v>
       </c>
       <c r="E6">
-        <v>0.09390000000000001</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1085,85 +1094,82 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>135.9</v>
+        <v>15.6</v>
       </c>
       <c r="L6">
-        <v>0.3976009362200117</v>
+        <v>0.1918819188191882</v>
       </c>
       <c r="M6">
-        <v>70.50239999999999</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.02695870296726828</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.5187814569536423</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>70.50239999999999</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.02695870296726828</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.5187814569536423</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>2780.6</v>
+        <v>666.1</v>
       </c>
       <c r="V6">
-        <v>1.063245640868767</v>
+        <v>3.600540540540541</v>
       </c>
       <c r="W6">
-        <v>0.08492688413948257</v>
+        <v>0.0477648499693815</v>
       </c>
       <c r="X6">
-        <v>0.077897193755947</v>
+        <v>0.1495311232718405</v>
       </c>
       <c r="Y6">
-        <v>0.00702969038353557</v>
+        <v>-0.101766273302459</v>
       </c>
       <c r="Z6">
-        <v>0.05412595607214683</v>
+        <v>0.08062276874256247</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.05585093040753479</v>
+        <v>0.05542260097920786</v>
       </c>
       <c r="AC6">
-        <v>-0.05585093040753479</v>
+        <v>-0.05542260097920786</v>
       </c>
       <c r="AD6">
-        <v>4688.6</v>
+        <v>1556.5</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>4688.6</v>
+        <v>1556.5</v>
       </c>
       <c r="AG6">
-        <v>1908</v>
+        <v>890.4</v>
       </c>
       <c r="AH6">
-        <v>0.6419398121525781</v>
+        <v>0.8937697387309791</v>
       </c>
       <c r="AI6">
-        <v>0.7387228410720194</v>
+        <v>0.8166316894018888</v>
       </c>
       <c r="AJ6">
-        <v>0.4218252564556067</v>
+        <v>0.8279709875395201</v>
       </c>
       <c r="AK6">
-        <v>0.5350082718784175</v>
+        <v>0.7181224292281635</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1180,7 +1186,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Banque Cantonale Vaudoise (SWX:BCVN)</t>
+          <t>Valiant Holding AG (SWX:VATN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1189,10 +1195,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0331</v>
+        <v>0.0672</v>
       </c>
       <c r="E7">
-        <v>0.055</v>
+        <v>0.0423</v>
+      </c>
+      <c r="F7">
+        <v>0.142</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1207,28 +1216,28 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>501.1</v>
+        <v>177.1</v>
       </c>
       <c r="L7">
-        <v>0.3884496124031008</v>
+        <v>0.2687813021702838</v>
       </c>
       <c r="M7">
-        <v>411.461</v>
+        <v>102.858</v>
       </c>
       <c r="N7">
-        <v>0.05199022011068712</v>
+        <v>0.05589197413465196</v>
       </c>
       <c r="O7">
-        <v>0.8211155457992416</v>
+        <v>0.5807905138339922</v>
       </c>
       <c r="P7">
-        <v>411.461</v>
+        <v>102.858</v>
       </c>
       <c r="Q7">
-        <v>0.05199022011068712</v>
+        <v>0.05589197413465196</v>
       </c>
       <c r="R7">
-        <v>0.8211155457992416</v>
+        <v>0.5807905138339922</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1237,55 +1246,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>13981.7</v>
+        <v>5030.9</v>
       </c>
       <c r="V7">
-        <v>1.766659927724849</v>
+        <v>2.733739064282997</v>
       </c>
       <c r="W7">
-        <v>0.1235636435370124</v>
+        <v>0.0641992314942362</v>
       </c>
       <c r="X7">
-        <v>0.08830402978874489</v>
+        <v>0.1378126807169845</v>
       </c>
       <c r="Y7">
-        <v>0.03525961374826748</v>
+        <v>-0.07361344922274829</v>
       </c>
       <c r="Z7">
-        <v>0.1501326753875518</v>
+        <v>0.07573389117491551</v>
       </c>
       <c r="AA7">
         <v>0</v>
       </c>
       <c r="AB7">
-        <v>0.05597654732662422</v>
+        <v>0.05546972455228043</v>
       </c>
       <c r="AC7">
-        <v>-0.05597654732662422</v>
+        <v>-0.05546972455228043</v>
       </c>
       <c r="AD7">
-        <v>21793.9</v>
+        <v>13490.8</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>21793.9</v>
+        <v>13490.8</v>
       </c>
       <c r="AG7">
-        <v>7812.200000000001</v>
+        <v>8459.9</v>
       </c>
       <c r="AH7">
-        <v>0.733601273726694</v>
+        <v>0.8799629511254901</v>
       </c>
       <c r="AI7">
-        <v>0.840839995061576</v>
+        <v>0.8126106807695551</v>
       </c>
       <c r="AJ7">
-        <v>0.4967570454776681</v>
+        <v>0.8213335663385177</v>
       </c>
       <c r="AK7">
-        <v>0.6544251308900524</v>
+        <v>0.7311358667000838</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1302,7 +1311,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Graubündner Kantonalbank (SWX:GRKP)</t>
+          <t>St. Galler Kantonalbank AG (SWX:SGKN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1311,11 +1320,11 @@
         </is>
       </c>
       <c r="D8">
+        <v>0.0314</v>
+      </c>
+      <c r="E8">
         <v>0.0449</v>
       </c>
-      <c r="E8">
-        <v>0.0553</v>
-      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -1323,94 +1332,103 @@
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>0.0003479715948439971</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>0.0002970358452135199</v>
       </c>
       <c r="K8">
-        <v>259.3</v>
+        <v>221.7</v>
       </c>
       <c r="L8">
-        <v>0.4656132160172383</v>
+        <v>0.3614870373389859</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>126.178</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.04370709065087118</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.5691384754172306</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>126.178</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.04370709065087118</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.5691384754172306</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>0</v>
+        <v>9318.4</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>3.227822231459351</v>
       </c>
       <c r="W8">
-        <v>0.08313028981790203</v>
+        <v>0.07115119227189576</v>
       </c>
       <c r="X8">
-        <v>0.07998492846293345</v>
+        <v>0.1111185358863634</v>
       </c>
       <c r="Y8">
-        <v>0.003145361354968582</v>
+        <v>-0.03996734361446769</v>
       </c>
       <c r="Z8">
-        <v>0.04601414548699474</v>
+        <v>0.0941786890765766</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>2.797444651096222E-05</v>
       </c>
       <c r="AB8">
-        <v>0.05621056750817096</v>
+        <v>0.05564203843899144</v>
       </c>
       <c r="AC8">
-        <v>-0.05621056750817096</v>
+        <v>-0.05561406399248048</v>
       </c>
       <c r="AD8">
-        <v>9502.9</v>
+        <v>14042.3</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>0.432945104410883</v>
       </c>
       <c r="AF8">
-        <v>9502.9</v>
+        <v>14042.73294510441</v>
       </c>
       <c r="AG8">
-        <v>9502.9</v>
+        <v>4724.33294510441</v>
       </c>
       <c r="AH8">
-        <v>0.6650593471810089</v>
+        <v>0.829476515565282</v>
       </c>
       <c r="AI8">
-        <v>0.7454541175732283</v>
+        <v>0.8134521694155601</v>
       </c>
       <c r="AJ8">
-        <v>0.6650593471810089</v>
+        <v>0.6207053415889904</v>
       </c>
       <c r="AK8">
-        <v>0.7454541175732283</v>
+        <v>0.5946496852377614</v>
       </c>
       <c r="AL8">
         <v>0</v>
       </c>
       <c r="AM8">
         <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>46807.66666666666</v>
+      </c>
+      <c r="AP8">
+        <v>15747.77648368137</v>
       </c>
     </row>
     <row r="9">
@@ -1421,117 +1439,968 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>Berner Kantonalbank AG (SWX:BEKN)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0634</v>
+      </c>
+      <c r="E9">
+        <v>0.0424</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>194.3</v>
+      </c>
+      <c r="L9">
+        <v>0.323563696919234</v>
+      </c>
+      <c r="M9">
+        <v>102.453</v>
+      </c>
+      <c r="N9">
+        <v>0.04278322963210424</v>
+      </c>
+      <c r="O9">
+        <v>0.5272928461142563</v>
+      </c>
+      <c r="P9">
+        <v>102.453</v>
+      </c>
+      <c r="Q9">
+        <v>0.04278322963210424</v>
+      </c>
+      <c r="R9">
+        <v>0.5272928461142563</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0</v>
+      </c>
+      <c r="U9">
+        <v>8513.700000000001</v>
+      </c>
+      <c r="V9">
+        <v>3.555226124357958</v>
+      </c>
+      <c r="W9">
+        <v>0.0627077618202356</v>
+      </c>
+      <c r="X9">
+        <v>0.1049737115021469</v>
+      </c>
+      <c r="Y9">
+        <v>-0.04226594968191127</v>
+      </c>
+      <c r="Z9">
+        <v>0.1546723676076654</v>
+      </c>
+      <c r="AA9">
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <v>0.05570442729305489</v>
+      </c>
+      <c r="AC9">
+        <v>-0.05570442729305489</v>
+      </c>
+      <c r="AD9">
+        <v>10288.9</v>
+      </c>
+      <c r="AE9">
+        <v>0</v>
+      </c>
+      <c r="AF9">
+        <v>10288.9</v>
+      </c>
+      <c r="AG9">
+        <v>1775.199999999999</v>
+      </c>
+      <c r="AH9">
+        <v>0.8111971364596803</v>
+      </c>
+      <c r="AI9">
+        <v>0.7614864264779894</v>
+      </c>
+      <c r="AJ9">
+        <v>0.4257176431089473</v>
+      </c>
+      <c r="AK9">
+        <v>0.3551891794553712</v>
+      </c>
+      <c r="AL9">
+        <v>0</v>
+      </c>
+      <c r="AM9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hypothekarbank Lenzburg AG (SWX:HBLN)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>0.063</v>
+      </c>
+      <c r="E10">
+        <v>-0.0108</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>22.4</v>
+      </c>
+      <c r="L10">
+        <v>0.1830065359477124</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>941.5</v>
+      </c>
+      <c r="V10">
+        <v>2.940349781386633</v>
+      </c>
+      <c r="W10">
+        <v>0.03589743589743589</v>
+      </c>
+      <c r="X10">
+        <v>0.09642736548377839</v>
+      </c>
+      <c r="Y10">
+        <v>-0.0605299295863425</v>
+      </c>
+      <c r="Z10">
+        <v>0.2314674735249622</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0.05581733373148488</v>
+      </c>
+      <c r="AC10">
+        <v>-0.05581733373148488</v>
+      </c>
+      <c r="AD10">
+        <v>1122.9</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>1122.9</v>
+      </c>
+      <c r="AG10">
+        <v>181.4000000000001</v>
+      </c>
+      <c r="AH10">
+        <v>0.7781165546393182</v>
+      </c>
+      <c r="AI10">
+        <v>0.6550195415038208</v>
+      </c>
+      <c r="AJ10">
+        <v>0.3616427432216907</v>
+      </c>
+      <c r="AK10">
+        <v>0.2347308488612837</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Zuger Kantonalbank (SWX:ZUGER)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.0848</v>
+      </c>
+      <c r="E11">
+        <v>0.09390000000000001</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>135.9</v>
+      </c>
+      <c r="L11">
+        <v>0.3976009362200117</v>
+      </c>
+      <c r="M11">
+        <v>70.50239999999999</v>
+      </c>
+      <c r="N11">
+        <v>0.02695870296726828</v>
+      </c>
+      <c r="O11">
+        <v>0.5187814569536423</v>
+      </c>
+      <c r="P11">
+        <v>70.50239999999999</v>
+      </c>
+      <c r="Q11">
+        <v>0.02695870296726828</v>
+      </c>
+      <c r="R11">
+        <v>0.5187814569536423</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>2780.6</v>
+      </c>
+      <c r="V11">
+        <v>1.063245640868767</v>
+      </c>
+      <c r="W11">
+        <v>0.08492688413948257</v>
+      </c>
+      <c r="X11">
+        <v>0.07787655811414049</v>
+      </c>
+      <c r="Y11">
+        <v>0.007050326025342085</v>
+      </c>
+      <c r="Z11">
+        <v>0.05412595607214683</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0.0558435416057532</v>
+      </c>
+      <c r="AC11">
+        <v>-0.0558435416057532</v>
+      </c>
+      <c r="AD11">
+        <v>4688.6</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>4688.6</v>
+      </c>
+      <c r="AG11">
+        <v>1908</v>
+      </c>
+      <c r="AH11">
+        <v>0.6419398121525781</v>
+      </c>
+      <c r="AI11">
+        <v>0.7387228410720194</v>
+      </c>
+      <c r="AJ11">
+        <v>0.4218252564556067</v>
+      </c>
+      <c r="AK11">
+        <v>0.5350082718784175</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Banque Cantonale Vaudoise (SWX:BCVN)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.0331</v>
+      </c>
+      <c r="E12">
+        <v>0.055</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>501.1</v>
+      </c>
+      <c r="L12">
+        <v>0.3884496124031008</v>
+      </c>
+      <c r="M12">
+        <v>411.461</v>
+      </c>
+      <c r="N12">
+        <v>0.05199022011068712</v>
+      </c>
+      <c r="O12">
+        <v>0.8211155457992416</v>
+      </c>
+      <c r="P12">
+        <v>411.461</v>
+      </c>
+      <c r="Q12">
+        <v>0.05199022011068712</v>
+      </c>
+      <c r="R12">
+        <v>0.8211155457992416</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>13981.7</v>
+      </c>
+      <c r="V12">
+        <v>1.766659927724849</v>
+      </c>
+      <c r="W12">
+        <v>0.1235636435370124</v>
+      </c>
+      <c r="X12">
+        <v>0.0882767034766466</v>
+      </c>
+      <c r="Y12">
+        <v>0.03528694006036578</v>
+      </c>
+      <c r="Z12">
+        <v>0.1501326753875518</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0.05596926763188748</v>
+      </c>
+      <c r="AC12">
+        <v>-0.05596926763188748</v>
+      </c>
+      <c r="AD12">
+        <v>21793.9</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>21793.9</v>
+      </c>
+      <c r="AG12">
+        <v>7812.200000000001</v>
+      </c>
+      <c r="AH12">
+        <v>0.733601273726694</v>
+      </c>
+      <c r="AI12">
+        <v>0.840839995061576</v>
+      </c>
+      <c r="AJ12">
+        <v>0.4967570454776681</v>
+      </c>
+      <c r="AK12">
+        <v>0.6544251308900524</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Graubündner Kantonalbank (SWX:GRKP)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.0449</v>
+      </c>
+      <c r="E13">
+        <v>0.0553</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>259.3</v>
+      </c>
+      <c r="L13">
+        <v>0.4656132160172383</v>
+      </c>
+      <c r="M13">
+        <v>-0</v>
+      </c>
+      <c r="N13">
+        <v>-0</v>
+      </c>
+      <c r="O13">
+        <v>-0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>-0</v>
+      </c>
+      <c r="R13">
+        <v>-0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.08313028981790203</v>
+      </c>
+      <c r="X13">
+        <v>0.07996295059333193</v>
+      </c>
+      <c r="Y13">
+        <v>0.003167339224570104</v>
+      </c>
+      <c r="Z13">
+        <v>0.04601414548699474</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0.05620320622617905</v>
+      </c>
+      <c r="AC13">
+        <v>-0.05620320622617905</v>
+      </c>
+      <c r="AD13">
+        <v>9502.9</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>9502.9</v>
+      </c>
+      <c r="AG13">
+        <v>9502.9</v>
+      </c>
+      <c r="AH13">
+        <v>0.6650593471810089</v>
+      </c>
+      <c r="AI13">
+        <v>0.7454541175732283</v>
+      </c>
+      <c r="AJ13">
+        <v>0.6650593471810089</v>
+      </c>
+      <c r="AK13">
+        <v>0.7454541175732283</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>Banque Cantonale de Genève SA (SWX:BCGE)</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Banks (Regional)</t>
         </is>
       </c>
-      <c r="D9">
+      <c r="D14">
         <v>0.06849999999999999</v>
       </c>
-      <c r="E9">
+      <c r="E14">
         <v>0.186</v>
       </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
         <v>256.4</v>
       </c>
-      <c r="L9">
+      <c r="L14">
         <v>0.3851584797957037</v>
       </c>
-      <c r="M9">
+      <c r="M14">
         <v>51.5499</v>
       </c>
-      <c r="N9">
+      <c r="N14">
         <v>0.02568249302510961</v>
       </c>
-      <c r="O9">
+      <c r="O14">
         <v>0.2010526521060843</v>
       </c>
-      <c r="P9">
+      <c r="P14">
         <v>51.5499</v>
       </c>
-      <c r="Q9">
+      <c r="Q14">
         <v>0.02568249302510961</v>
       </c>
-      <c r="R9">
+      <c r="R14">
         <v>0.2010526521060843</v>
       </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
-      <c r="U9">
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
         <v>7716.8</v>
       </c>
-      <c r="V9">
+      <c r="V14">
         <v>3.844559585492228</v>
       </c>
-      <c r="W9">
+      <c r="W14">
         <v>0.1114879554743891</v>
       </c>
-      <c r="X9">
-        <v>0.1112419599028084</v>
-      </c>
-      <c r="Y9">
-        <v>0.000245995571580615</v>
-      </c>
-      <c r="Z9">
+      <c r="X14">
+        <v>0.1111998865410704</v>
+      </c>
+      <c r="Y14">
+        <v>0.0002880689333187025</v>
+      </c>
+      <c r="Z14">
         <v>0.2391851106639838</v>
       </c>
-      <c r="AA9">
-        <v>0</v>
-      </c>
-      <c r="AB9">
-        <v>0.05635701807727175</v>
-      </c>
-      <c r="AC9">
-        <v>-0.05635701807727175</v>
-      </c>
-      <c r="AD9">
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0.05634985276518861</v>
+      </c>
+      <c r="AC14">
+        <v>-0.05634985276518861</v>
+      </c>
+      <c r="AD14">
         <v>9778.700000000001</v>
       </c>
-      <c r="AE9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
         <v>9778.700000000001</v>
       </c>
-      <c r="AG9">
+      <c r="AG14">
         <v>2061.900000000001</v>
       </c>
-      <c r="AH9">
+      <c r="AH14">
         <v>0.8296948048091363</v>
       </c>
-      <c r="AI9">
+      <c r="AI14">
         <v>0.796246234020031</v>
       </c>
-      <c r="AJ9">
+      <c r="AJ14">
         <v>0.5067213880219213</v>
       </c>
-      <c r="AK9">
+      <c r="AK14">
         <v>0.4517549625345078</v>
       </c>
-      <c r="AL9">
-        <v>0</v>
-      </c>
-      <c r="AM9">
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Walliser Kantonalbank (SWX:WKBN)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>0.0433</v>
+      </c>
+      <c r="E15">
+        <v>0.0599</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>-0.0001652790417151443</v>
+      </c>
+      <c r="J15">
+        <v>-0.0001366054272768377</v>
+      </c>
+      <c r="K15">
+        <v>100.9</v>
+      </c>
+      <c r="L15">
+        <v>0.3019150209455416</v>
+      </c>
+      <c r="M15">
+        <v>-0</v>
+      </c>
+      <c r="N15">
+        <v>-0</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>-0</v>
+      </c>
+      <c r="R15">
+        <v>-0</v>
+      </c>
+      <c r="S15">
+        <v>0</v>
+      </c>
+      <c r="U15">
+        <v>3766.7</v>
+      </c>
+      <c r="V15">
+        <v>1.979556443136431</v>
+      </c>
+      <c r="W15">
+        <v>0.06031081888822475</v>
+      </c>
+      <c r="X15">
+        <v>0.101695120023337</v>
+      </c>
+      <c r="Y15">
+        <v>-0.04138430113511224</v>
+      </c>
+      <c r="Z15">
+        <v>0.06516631805741464</v>
+      </c>
+      <c r="AA15">
+        <v>-8.902072722291432E-06</v>
+      </c>
+      <c r="AB15">
+        <v>0.05984140516505135</v>
+      </c>
+      <c r="AC15">
+        <v>-0.05985030723777364</v>
+      </c>
+      <c r="AD15">
+        <v>7598.5</v>
+      </c>
+      <c r="AE15">
+        <v>0.5161812787060061</v>
+      </c>
+      <c r="AF15">
+        <v>7599.016181278706</v>
+      </c>
+      <c r="AG15">
+        <v>3832.316181278707</v>
+      </c>
+      <c r="AH15">
+        <v>0.7997435475810342</v>
+      </c>
+      <c r="AI15">
+        <v>0.8126233031049015</v>
+      </c>
+      <c r="AJ15">
+        <v>0.6682194501636495</v>
+      </c>
+      <c r="AK15">
+        <v>0.6862396055232143</v>
+      </c>
+      <c r="AL15">
+        <v>0</v>
+      </c>
+      <c r="AM15">
+        <v>0</v>
+      </c>
+      <c r="AN15">
+        <v>158302.0833333333</v>
+      </c>
+      <c r="AP15">
+        <v>79839.92044330639</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Thurgauer Kantonalbank (SWX:TKBP)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Banks (Regional)</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>0.0432</v>
+      </c>
+      <c r="E16">
+        <v>0.0369</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>178</v>
+      </c>
+      <c r="L16">
+        <v>0.3819742489270386</v>
+      </c>
+      <c r="M16">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="N16">
+        <v>0.02618622904031395</v>
+      </c>
+      <c r="O16">
+        <v>0.4123595505617978</v>
+      </c>
+      <c r="P16">
+        <v>73.40000000000001</v>
+      </c>
+      <c r="Q16">
+        <v>0.02618622904031395</v>
+      </c>
+      <c r="R16">
+        <v>0.4123595505617978</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>5093.1</v>
+      </c>
+      <c r="V16">
+        <v>1.817017481270068</v>
+      </c>
+      <c r="W16">
+        <v>0.06128210424843352</v>
+      </c>
+      <c r="X16">
+        <v>0.1094392459035646</v>
+      </c>
+      <c r="Y16">
+        <v>-0.04815714165513105</v>
+      </c>
+      <c r="Z16">
+        <v>0.0490438553101024</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0.05988434688569376</v>
+      </c>
+      <c r="AC16">
+        <v>-0.05988434688569376</v>
+      </c>
+      <c r="AD16">
+        <v>13199.7</v>
+      </c>
+      <c r="AE16">
+        <v>0</v>
+      </c>
+      <c r="AF16">
+        <v>13199.7</v>
+      </c>
+      <c r="AG16">
+        <v>8106.6</v>
+      </c>
+      <c r="AH16">
+        <v>0.8248420579027289</v>
+      </c>
+      <c r="AI16">
+        <v>0.8131298819702831</v>
+      </c>
+      <c r="AJ16">
+        <v>0.7430703233849087</v>
+      </c>
+      <c r="AK16">
+        <v>0.727695442590282</v>
+      </c>
+      <c r="AL16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
         <v>0</v>
       </c>
     </row>
